--- a/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
+++ b/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
@@ -670,136 +670,132 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="32">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1058,137 +1054,137 @@
   <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="n">
+      <c r="B4" s="5" t="n">
         <v>95000</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="5" t="n">
         <v>120000</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="6" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="5" t="n">
         <v>155000</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="5" t="n">
         <v>185000</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="6" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="7" t="n">
         <v>0.22</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="6" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="7" t="n">
         <v>0.12</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B11" s="9" t="n">
+      <c r="B11" s="8" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="6" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="6" t="n">
+      <c r="B12" s="5" t="n">
         <v>722514.4</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="6" t="n">
+      <c r="B13" s="5" t="n">
         <v>128375</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="6" t="s">
         <v>21</v>
       </c>
     </row>
@@ -1212,1231 +1208,1231 @@
   <dimension ref="A1:R23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="11" t="n">
+      <c r="B5" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C5" s="11" t="n">
+      <c r="C5" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E5" s="11" t="n">
+      <c r="E5" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="L5" s="11" t="n">
+      <c r="L5" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="O5" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="P5" s="11" t="n">
+      <c r="P5" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="10" t="s">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="11" t="n">
         <v>1107883.476</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>1130224.27392</v>
       </c>
-      <c r="D6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>1470581.13731659</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>2128361.5241759</v>
       </c>
-      <c r="F6" s="12" t="n">
+      <c r="F6" s="11" t="n">
         <v>2531696.60117519</v>
       </c>
-      <c r="G6" s="12" t="n">
+      <c r="G6" s="11" t="n">
         <v>2960567.60023987</v>
       </c>
-      <c r="H6" s="12" t="n">
+      <c r="H6" s="11" t="n">
         <v>3415973.30476096</v>
       </c>
-      <c r="I6" s="12" t="n">
+      <c r="I6" s="11" t="n">
         <v>3898958.3702101</v>
       </c>
-      <c r="J6" s="12" t="n">
+      <c r="J6" s="11" t="n">
         <v>4410614.70976327</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="11" t="n">
         <v>4952082.94628947</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="11" t="n">
         <v>5524553.93215493</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="11" t="n">
         <v>6129270.33838766</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="11" t="n">
         <v>6767528.314843</v>
       </c>
-      <c r="O6" s="12" t="n">
+      <c r="O6" s="11" t="n">
         <v>7045784.99129078</v>
       </c>
-      <c r="P6" s="12" t="n">
+      <c r="P6" s="11" t="n">
         <v>7328447.27269707</v>
       </c>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="13" t="n">
+      <c r="B7" s="12" t="n">
         <f aca="false">IF(B6&gt;=6000000,'Your numbers'!$B$7,IF(B6&gt;=3000000,'Your numbers'!$B$6,IF(B6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>95000</v>
       </c>
-      <c r="C7" s="13" t="n">
+      <c r="C7" s="12" t="n">
         <f aca="false">IF(C6&gt;=6000000,'Your numbers'!$B$7,IF(C6&gt;=3000000,'Your numbers'!$B$6,IF(C6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>95000</v>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <f aca="false">IF(D6&gt;=6000000,'Your numbers'!$B$7,IF(D6&gt;=3000000,'Your numbers'!$B$6,IF(D6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>95000</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="12" t="n">
         <f aca="false">IF(E6&gt;=6000000,'Your numbers'!$B$7,IF(E6&gt;=3000000,'Your numbers'!$B$6,IF(E6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>120000</v>
       </c>
-      <c r="F7" s="13" t="n">
+      <c r="F7" s="12" t="n">
         <f aca="false">IF(F6&gt;=6000000,'Your numbers'!$B$7,IF(F6&gt;=3000000,'Your numbers'!$B$6,IF(F6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>120000</v>
       </c>
-      <c r="G7" s="13" t="n">
+      <c r="G7" s="12" t="n">
         <f aca="false">IF(G6&gt;=6000000,'Your numbers'!$B$7,IF(G6&gt;=3000000,'Your numbers'!$B$6,IF(G6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>120000</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
         <f aca="false">IF(H6&gt;=6000000,'Your numbers'!$B$7,IF(H6&gt;=3000000,'Your numbers'!$B$6,IF(H6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>155000</v>
       </c>
-      <c r="I7" s="13" t="n">
+      <c r="I7" s="12" t="n">
         <f aca="false">IF(I6&gt;=6000000,'Your numbers'!$B$7,IF(I6&gt;=3000000,'Your numbers'!$B$6,IF(I6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>155000</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="12" t="n">
         <f aca="false">IF(J6&gt;=6000000,'Your numbers'!$B$7,IF(J6&gt;=3000000,'Your numbers'!$B$6,IF(J6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>155000</v>
       </c>
-      <c r="K7" s="13" t="n">
+      <c r="K7" s="12" t="n">
         <f aca="false">IF(K6&gt;=6000000,'Your numbers'!$B$7,IF(K6&gt;=3000000,'Your numbers'!$B$6,IF(K6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>155000</v>
       </c>
-      <c r="L7" s="13" t="n">
+      <c r="L7" s="12" t="n">
         <f aca="false">IF(L6&gt;=6000000,'Your numbers'!$B$7,IF(L6&gt;=3000000,'Your numbers'!$B$6,IF(L6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>155000</v>
       </c>
-      <c r="M7" s="13" t="n">
+      <c r="M7" s="12" t="n">
         <f aca="false">IF(M6&gt;=6000000,'Your numbers'!$B$7,IF(M6&gt;=3000000,'Your numbers'!$B$6,IF(M6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>185000</v>
       </c>
-      <c r="N7" s="13" t="n">
+      <c r="N7" s="12" t="n">
         <f aca="false">IF(N6&gt;=6000000,'Your numbers'!$B$7,IF(N6&gt;=3000000,'Your numbers'!$B$6,IF(N6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>185000</v>
       </c>
-      <c r="O7" s="13" t="n">
+      <c r="O7" s="12" t="n">
         <f aca="false">IF(O6&gt;=6000000,'Your numbers'!$B$7,IF(O6&gt;=3000000,'Your numbers'!$B$6,IF(O6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>185000</v>
       </c>
-      <c r="P7" s="13" t="n">
+      <c r="P7" s="12" t="n">
         <f aca="false">IF(P6&gt;=6000000,'Your numbers'!$B$7,IF(P6&gt;=3000000,'Your numbers'!$B$6,IF(P6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
         <v>185000</v>
       </c>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="7" t="s">
+      <c r="Q7" s="2"/>
+      <c r="R7" s="6" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="12" t="n">
         <f aca="false">B7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>20900</v>
       </c>
-      <c r="C8" s="13" t="n">
+      <c r="C8" s="12" t="n">
         <f aca="false">C7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>20900</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">D7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>20900</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="12" t="n">
         <f aca="false">E7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>26400</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="12" t="n">
         <f aca="false">F7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>26400</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="12" t="n">
         <f aca="false">G7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>26400</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="H8" s="12" t="n">
         <f aca="false">H7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>34100</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="I8" s="12" t="n">
         <f aca="false">I7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>34100</v>
       </c>
-      <c r="J8" s="13" t="n">
+      <c r="J8" s="12" t="n">
         <f aca="false">J7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>34100</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="K8" s="12" t="n">
         <f aca="false">K7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>34100</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="L8" s="12" t="n">
         <f aca="false">L7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>34100</v>
       </c>
-      <c r="M8" s="13" t="n">
+      <c r="M8" s="12" t="n">
         <f aca="false">M7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>40700</v>
       </c>
-      <c r="N8" s="13" t="n">
+      <c r="N8" s="12" t="n">
         <f aca="false">N7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>40700</v>
       </c>
-      <c r="O8" s="13" t="n">
+      <c r="O8" s="12" t="n">
         <f aca="false">O7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>40700</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="P8" s="12" t="n">
         <f aca="false">P7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
         <v>40700</v>
       </c>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <f aca="false">B7+B8</f>
         <v>115900</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <f aca="false">C7+C8</f>
         <v>115900</v>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="11" t="n">
         <f aca="false">D7+D8</f>
         <v>115900</v>
       </c>
-      <c r="E9" s="12" t="n">
+      <c r="E9" s="11" t="n">
         <f aca="false">E7+E8</f>
         <v>146400</v>
       </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
         <f aca="false">F7+F8</f>
         <v>146400</v>
       </c>
-      <c r="G9" s="12" t="n">
+      <c r="G9" s="11" t="n">
         <f aca="false">G7+G8</f>
         <v>146400</v>
       </c>
-      <c r="H9" s="12" t="n">
+      <c r="H9" s="11" t="n">
         <f aca="false">H7+H8</f>
         <v>189100</v>
       </c>
-      <c r="I9" s="12" t="n">
+      <c r="I9" s="11" t="n">
         <f aca="false">I7+I8</f>
         <v>189100</v>
       </c>
-      <c r="J9" s="12" t="n">
+      <c r="J9" s="11" t="n">
         <f aca="false">J7+J8</f>
         <v>189100</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K9" s="11" t="n">
         <f aca="false">K7+K8</f>
         <v>189100</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="11" t="n">
         <f aca="false">L7+L8</f>
         <v>189100</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="11" t="n">
         <f aca="false">M7+M8</f>
         <v>225700</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" s="11" t="n">
         <f aca="false">N7+N8</f>
         <v>225700</v>
       </c>
-      <c r="O9" s="12" t="n">
+      <c r="O9" s="11" t="n">
         <f aca="false">O7+O8</f>
         <v>225700</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="11" t="n">
         <f aca="false">P7+P8</f>
         <v>225700</v>
       </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C10" s="13" t="n">
+      <c r="C10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D10" s="13" t="n">
+      <c r="D10" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="12" t="n">
         <v>79827.687</v>
       </c>
-      <c r="F10" s="13" t="n">
+      <c r="F10" s="12" t="n">
         <v>82621.656045</v>
       </c>
-      <c r="G10" s="13" t="n">
+      <c r="G10" s="12" t="n">
         <v>85513.414006575</v>
       </c>
-      <c r="H10" s="13" t="n">
+      <c r="H10" s="12" t="n">
         <v>88506.3834968051</v>
       </c>
-      <c r="I10" s="13" t="n">
+      <c r="I10" s="12" t="n">
         <v>91604.1069191933</v>
       </c>
-      <c r="J10" s="13" t="n">
+      <c r="J10" s="12" t="n">
         <v>94810.250661365</v>
       </c>
-      <c r="K10" s="13" t="n">
+      <c r="K10" s="12" t="n">
         <v>98128.6094345128</v>
       </c>
-      <c r="L10" s="13" t="n">
+      <c r="L10" s="12" t="n">
         <v>101563.110764721</v>
       </c>
-      <c r="M10" s="13" t="n">
+      <c r="M10" s="12" t="n">
         <v>105117.819641486</v>
       </c>
-      <c r="N10" s="13" t="n">
+      <c r="N10" s="12" t="n">
         <v>108796.943328938</v>
       </c>
-      <c r="O10" s="13" t="n">
+      <c r="O10" s="12" t="n">
         <v>112604.836345451</v>
       </c>
-      <c r="P10" s="13" t="n">
+      <c r="P10" s="12" t="n">
         <v>116546.005617542</v>
       </c>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="7" t="s">
+      <c r="Q10" s="2"/>
+      <c r="R10" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="12" t="n">
+      <c r="B11" s="11" t="n">
         <f aca="false">B9-B10</f>
         <v>115900</v>
       </c>
-      <c r="C11" s="12" t="n">
+      <c r="C11" s="11" t="n">
         <f aca="false">C9-C10</f>
         <v>115900</v>
       </c>
-      <c r="D11" s="12" t="n">
+      <c r="D11" s="11" t="n">
         <f aca="false">D9-D10</f>
         <v>115900</v>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="E11" s="11" t="n">
         <f aca="false">E9-E10</f>
         <v>66572.313</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="F11" s="11" t="n">
         <f aca="false">F9-F10</f>
         <v>63778.343955</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <f aca="false">G9-G10</f>
         <v>60886.585993425</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="11" t="n">
         <f aca="false">H9-H10</f>
         <v>100593.616503195</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="I11" s="11" t="n">
         <f aca="false">I9-I10</f>
         <v>97495.8930808067</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="J11" s="11" t="n">
         <f aca="false">J9-J10</f>
         <v>94289.749338635</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="K11" s="11" t="n">
         <f aca="false">K9-K10</f>
         <v>90971.3905654872</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="L11" s="11" t="n">
         <f aca="false">L9-L10</f>
         <v>87536.889235279</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="M11" s="11" t="n">
         <f aca="false">M9-M10</f>
         <v>120582.180358514</v>
       </c>
-      <c r="N11" s="12" t="n">
+      <c r="N11" s="11" t="n">
         <f aca="false">N9-N10</f>
         <v>116903.056671062</v>
       </c>
-      <c r="O11" s="12" t="n">
+      <c r="O11" s="11" t="n">
         <f aca="false">O9-O10</f>
         <v>113095.163654549</v>
       </c>
-      <c r="P11" s="12" t="n">
+      <c r="P11" s="11" t="n">
         <f aca="false">P9-P10</f>
         <v>109153.994382458</v>
       </c>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
-      <c r="K12" s="15"/>
-      <c r="L12" s="15"/>
-      <c r="M12" s="15"/>
-      <c r="N12" s="15"/>
-      <c r="O12" s="15"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="15"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
+      <c r="O12" s="14"/>
+      <c r="P12" s="14"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="14"/>
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B13" s="16" t="n">
+      <c r="B13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,1/'Your numbers'!$B$11))</f>
         <v>0.25</v>
       </c>
-      <c r="C13" s="16" t="n">
+      <c r="C13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,2/'Your numbers'!$B$11))</f>
         <v>0.5</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,3/'Your numbers'!$B$11))</f>
         <v>0.75</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,4/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,5/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,6/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="H13" s="16" t="n">
+      <c r="H13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,7/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="I13" s="16" t="n">
+      <c r="I13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,8/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="J13" s="16" t="n">
+      <c r="J13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,9/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="K13" s="16" t="n">
+      <c r="K13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,10/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="L13" s="16" t="n">
+      <c r="L13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,11/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="M13" s="16" t="n">
+      <c r="M13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,12/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="N13" s="16" t="n">
+      <c r="N13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,13/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="O13" s="16" t="n">
+      <c r="O13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,14/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="P13" s="16" t="n">
+      <c r="P13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,15/'Your numbers'!$B$11))</f>
         <v>1</v>
       </c>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="7" t="s">
+      <c r="Q13" s="2"/>
+      <c r="R13" s="6" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="17" t="n">
+      <c r="B14" s="16" t="n">
         <f aca="false">B13*'Your numbers'!$B$10</f>
         <v>0.03</v>
       </c>
-      <c r="C14" s="17" t="n">
+      <c r="C14" s="16" t="n">
         <f aca="false">C13*'Your numbers'!$B$10</f>
         <v>0.06</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">D13*'Your numbers'!$B$10</f>
         <v>0.09</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">E13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="16" t="n">
         <f aca="false">F13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="16" t="n">
         <f aca="false">G13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="H14" s="17" t="n">
+      <c r="H14" s="16" t="n">
         <f aca="false">H13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="I14" s="17" t="n">
+      <c r="I14" s="16" t="n">
         <f aca="false">I13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="J14" s="17" t="n">
+      <c r="J14" s="16" t="n">
         <f aca="false">J13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="K14" s="17" t="n">
+      <c r="K14" s="16" t="n">
         <f aca="false">K13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="L14" s="17" t="n">
+      <c r="L14" s="16" t="n">
         <f aca="false">L13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="M14" s="17" t="n">
+      <c r="M14" s="16" t="n">
         <f aca="false">M13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="N14" s="17" t="n">
+      <c r="N14" s="16" t="n">
         <f aca="false">N13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="O14" s="17" t="n">
+      <c r="O14" s="16" t="n">
         <f aca="false">O13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="P14" s="17" t="n">
+      <c r="P14" s="16" t="n">
         <f aca="false">P13*'Your numbers'!$B$10</f>
         <v>0.12</v>
       </c>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="13" t="n">
-        <v>722514.397345807</v>
-      </c>
-      <c r="C15" s="13" t="n">
-        <v>814784.283227823</v>
-      </c>
-      <c r="D15" s="13" t="n">
-        <v>1019423.92033104</v>
-      </c>
-      <c r="E15" s="13" t="n">
-        <v>1867217.68455785</v>
-      </c>
-      <c r="F15" s="13" t="n">
-        <v>1982323.55921217</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <v>2066998.57190214</v>
-      </c>
-      <c r="H15" s="13" t="n">
-        <v>2784973.43382394</v>
-      </c>
-      <c r="I15" s="13" t="n">
-        <v>3588363.68812422</v>
-      </c>
-      <c r="J15" s="13" t="n">
-        <v>4480151.48996621</v>
-      </c>
-      <c r="K15" s="13" t="n">
-        <v>4863505.48237858</v>
-      </c>
-      <c r="L15" s="13" t="n">
-        <v>7857544.27315891</v>
-      </c>
-      <c r="M15" s="13" t="n">
-        <v>9340457.46435439</v>
-      </c>
-      <c r="N15" s="13" t="n">
-        <v>10942353.2656805</v>
-      </c>
-      <c r="O15" s="13" t="n">
-        <v>11949731.8634761</v>
-      </c>
-      <c r="P15" s="13" t="n">
-        <v>12958190.7073309</v>
-      </c>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="3"/>
+      <c r="B15" s="12" t="n">
+        <v>691314.397345807</v>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>752384.283227823</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>925823.920331045</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>1742417.68455785</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>1826323.55921217</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>1879798.57190215</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>2566573.43382394</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>3338763.68812422</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>4199351.48996621</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>4551505.48237858</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>7514344.27315891</v>
+      </c>
+      <c r="M15" s="12" t="n">
+        <v>8966057.46435439</v>
+      </c>
+      <c r="N15" s="12" t="n">
+        <v>10536753.2656805</v>
+      </c>
+      <c r="O15" s="12" t="n">
+        <v>11512931.8634761</v>
+      </c>
+      <c r="P15" s="12" t="n">
+        <v>12490190.7073309</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <f aca="false">MAX(0,B15-'Your numbers'!$B$12)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="12" t="n">
         <f aca="false">MAX(0,C15-'Your numbers'!$B$12)</f>
-        <v>92269.883227823</v>
-      </c>
-      <c r="D16" s="13" t="n">
+        <v>29869.883227823</v>
+      </c>
+      <c r="D16" s="12" t="n">
         <f aca="false">MAX(0,D15-'Your numbers'!$B$12)</f>
-        <v>296909.52033104</v>
-      </c>
-      <c r="E16" s="13" t="n">
+        <v>203309.520331045</v>
+      </c>
+      <c r="E16" s="12" t="n">
         <f aca="false">MAX(0,E15-'Your numbers'!$B$12)</f>
-        <v>1144703.28455785</v>
-      </c>
-      <c r="F16" s="13" t="n">
+        <v>1019903.28455785</v>
+      </c>
+      <c r="F16" s="12" t="n">
         <f aca="false">MAX(0,F15-'Your numbers'!$B$12)</f>
-        <v>1259809.15921217</v>
-      </c>
-      <c r="G16" s="13" t="n">
+        <v>1103809.15921217</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <f aca="false">MAX(0,G15-'Your numbers'!$B$12)</f>
-        <v>1344484.17190214</v>
-      </c>
-      <c r="H16" s="13" t="n">
+        <v>1157284.17190215</v>
+      </c>
+      <c r="H16" s="12" t="n">
         <f aca="false">MAX(0,H15-'Your numbers'!$B$12)</f>
-        <v>2062459.03382394</v>
-      </c>
-      <c r="I16" s="13" t="n">
+        <v>1844059.03382394</v>
+      </c>
+      <c r="I16" s="12" t="n">
         <f aca="false">MAX(0,I15-'Your numbers'!$B$12)</f>
-        <v>2865849.28812422</v>
-      </c>
-      <c r="J16" s="13" t="n">
+        <v>2616249.28812422</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <f aca="false">MAX(0,J15-'Your numbers'!$B$12)</f>
-        <v>3757637.08996621</v>
-      </c>
-      <c r="K16" s="13" t="n">
+        <v>3476837.08996621</v>
+      </c>
+      <c r="K16" s="12" t="n">
         <f aca="false">MAX(0,K15-'Your numbers'!$B$12)</f>
-        <v>4140991.08237858</v>
-      </c>
-      <c r="L16" s="13" t="n">
+        <v>3828991.08237858</v>
+      </c>
+      <c r="L16" s="12" t="n">
         <f aca="false">MAX(0,L15-'Your numbers'!$B$12)</f>
-        <v>7135029.87315891</v>
-      </c>
-      <c r="M16" s="13" t="n">
+        <v>6791829.87315891</v>
+      </c>
+      <c r="M16" s="12" t="n">
         <f aca="false">MAX(0,M15-'Your numbers'!$B$12)</f>
-        <v>8617943.06435439</v>
-      </c>
-      <c r="N16" s="13" t="n">
+        <v>8243543.06435439</v>
+      </c>
+      <c r="N16" s="12" t="n">
         <f aca="false">MAX(0,N15-'Your numbers'!$B$12)</f>
-        <v>10219838.8656805</v>
-      </c>
-      <c r="O16" s="13" t="n">
+        <v>9814238.8656805</v>
+      </c>
+      <c r="O16" s="12" t="n">
         <f aca="false">MAX(0,O15-'Your numbers'!$B$12)</f>
-        <v>11227217.4634761</v>
-      </c>
-      <c r="P16" s="13" t="n">
+        <v>10790417.4634761</v>
+      </c>
+      <c r="P16" s="12" t="n">
         <f aca="false">MAX(0,P15-'Your numbers'!$B$12)</f>
-        <v>12235676.3073309</v>
-      </c>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
+        <v>11767676.3073309</v>
+      </c>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="12" t="n">
+      <c r="B17" s="11" t="n">
         <f aca="false">B14*B16</f>
         <v>0</v>
       </c>
-      <c r="C17" s="12" t="n">
+      <c r="C17" s="11" t="n">
         <f aca="false">C14*C16</f>
-        <v>5536.19299366938</v>
-      </c>
-      <c r="D17" s="12" t="n">
+        <v>1792.19299366938</v>
+      </c>
+      <c r="D17" s="11" t="n">
         <f aca="false">D14*D16</f>
-        <v>26721.8568297936</v>
-      </c>
-      <c r="E17" s="12" t="n">
+        <v>18297.8568297941</v>
+      </c>
+      <c r="E17" s="11" t="n">
         <f aca="false">E14*E16</f>
-        <v>137364.394146942</v>
-      </c>
-      <c r="F17" s="12" t="n">
+        <v>122388.394146942</v>
+      </c>
+      <c r="F17" s="11" t="n">
         <f aca="false">F14*F16</f>
-        <v>151177.09910546</v>
-      </c>
-      <c r="G17" s="12" t="n">
+        <v>132457.09910546</v>
+      </c>
+      <c r="G17" s="11" t="n">
         <f aca="false">G14*G16</f>
-        <v>161338.100628257</v>
-      </c>
-      <c r="H17" s="12" t="n">
+        <v>138874.100628258</v>
+      </c>
+      <c r="H17" s="11" t="n">
         <f aca="false">H14*H16</f>
-        <v>247495.084058873</v>
-      </c>
-      <c r="I17" s="12" t="n">
+        <v>221287.084058873</v>
+      </c>
+      <c r="I17" s="11" t="n">
         <f aca="false">I14*I16</f>
-        <v>343901.914574906</v>
-      </c>
-      <c r="J17" s="12" t="n">
+        <v>313949.914574906</v>
+      </c>
+      <c r="J17" s="11" t="n">
         <f aca="false">J14*J16</f>
-        <v>450916.450795945</v>
-      </c>
-      <c r="K17" s="12" t="n">
+        <v>417220.450795945</v>
+      </c>
+      <c r="K17" s="11" t="n">
         <f aca="false">K14*K16</f>
-        <v>496918.92988543</v>
-      </c>
-      <c r="L17" s="12" t="n">
+        <v>459478.92988543</v>
+      </c>
+      <c r="L17" s="11" t="n">
         <f aca="false">L14*L16</f>
-        <v>856203.584779069</v>
-      </c>
-      <c r="M17" s="12" t="n">
+        <v>815019.584779069</v>
+      </c>
+      <c r="M17" s="11" t="n">
         <f aca="false">M14*M16</f>
-        <v>1034153.16772253</v>
-      </c>
-      <c r="N17" s="12" t="n">
+        <v>989225.167722527</v>
+      </c>
+      <c r="N17" s="11" t="n">
         <f aca="false">N14*N16</f>
-        <v>1226380.66388166</v>
-      </c>
-      <c r="O17" s="12" t="n">
+        <v>1177708.66388166</v>
+      </c>
+      <c r="O17" s="11" t="n">
         <f aca="false">O14*O16</f>
-        <v>1347266.09561713</v>
-      </c>
-      <c r="P17" s="12" t="n">
+        <v>1294850.09561713</v>
+      </c>
+      <c r="P17" s="11" t="n">
         <f aca="false">P14*P16</f>
-        <v>1468281.15687971</v>
-      </c>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
+        <v>1412121.15687971</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="19"/>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
-      <c r="K18" s="19"/>
-      <c r="L18" s="19"/>
-      <c r="M18" s="19"/>
-      <c r="N18" s="19"/>
-      <c r="O18" s="19"/>
-      <c r="P18" s="19"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="19"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
+      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
+      <c r="L18" s="18"/>
+      <c r="M18" s="18"/>
+      <c r="N18" s="18"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="18"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="13" t="n">
+      <c r="B19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^0</f>
         <v>128375</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^1</f>
         <v>131905.3125</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^2</f>
         <v>135532.70859375</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^3</f>
         <v>139259.858080078</v>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^4</f>
         <v>143089.50417728</v>
       </c>
-      <c r="G19" s="13" t="n">
+      <c r="G19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^5</f>
         <v>147024.465542156</v>
       </c>
-      <c r="H19" s="13" t="n">
+      <c r="H19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^6</f>
         <v>151067.638344565</v>
       </c>
-      <c r="I19" s="13" t="n">
+      <c r="I19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^7</f>
         <v>155221.99839904</v>
       </c>
-      <c r="J19" s="13" t="n">
+      <c r="J19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^8</f>
         <v>159490.603355014</v>
       </c>
-      <c r="K19" s="13" t="n">
+      <c r="K19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^9</f>
         <v>163876.594947277</v>
       </c>
-      <c r="L19" s="13" t="n">
+      <c r="L19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^10</f>
         <v>168383.201308327</v>
       </c>
-      <c r="M19" s="13" t="n">
+      <c r="M19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^11</f>
         <v>173013.739344306</v>
       </c>
-      <c r="N19" s="13" t="n">
+      <c r="N19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^12</f>
         <v>177771.617176274</v>
       </c>
-      <c r="O19" s="13" t="n">
+      <c r="O19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^13</f>
         <v>182660.336648622</v>
       </c>
-      <c r="P19" s="13" t="n">
+      <c r="P19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^14</f>
         <v>187683.495906459</v>
       </c>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="7" t="s">
+      <c r="Q19" s="2"/>
+      <c r="R19" s="6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="11" t="n">
         <f aca="false">B9-B19</f>
         <v>-12475</v>
       </c>
-      <c r="C20" s="12" t="n">
+      <c r="C20" s="11" t="n">
         <f aca="false">C9-C19</f>
         <v>-16005.3125</v>
       </c>
-      <c r="D20" s="12" t="n">
+      <c r="D20" s="11" t="n">
         <f aca="false">D9-D19</f>
         <v>-19632.70859375</v>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="E20" s="11" t="n">
         <f aca="false">E9-E19</f>
         <v>7140.14191992185</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="F20" s="11" t="n">
         <f aca="false">F9-F19</f>
         <v>3310.49582271971</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="G20" s="11" t="n">
         <f aca="false">G9-G19</f>
         <v>-624.465542155551</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="H20" s="11" t="n">
         <f aca="false">H9-H19</f>
         <v>38032.3616554352</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="I20" s="11" t="n">
         <f aca="false">I9-I19</f>
         <v>33878.0016009596</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="J20" s="11" t="n">
         <f aca="false">J9-J19</f>
         <v>29609.396644986</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="K20" s="11" t="n">
         <f aca="false">K9-K19</f>
         <v>25223.4050527231</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="L20" s="11" t="n">
         <f aca="false">L9-L19</f>
         <v>20716.798691673</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="M20" s="11" t="n">
         <f aca="false">M9-M19</f>
         <v>52686.260655694</v>
       </c>
-      <c r="N20" s="12" t="n">
+      <c r="N20" s="11" t="n">
         <f aca="false">N9-N19</f>
         <v>47928.3828237256</v>
       </c>
-      <c r="O20" s="12" t="n">
+      <c r="O20" s="11" t="n">
         <f aca="false">O9-O19</f>
         <v>43039.663351378</v>
       </c>
-      <c r="P20" s="12" t="n">
+      <c r="P20" s="11" t="n">
         <f aca="false">P9-P19</f>
         <v>38016.5040935409</v>
       </c>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="7" t="s">
+      <c r="Q20" s="2"/>
+      <c r="R20" s="6" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="B21" s="12" t="n">
+      <c r="B21" s="11" t="n">
         <f aca="false">B20</f>
         <v>-12475</v>
       </c>
-      <c r="C21" s="12" t="n">
+      <c r="C21" s="11" t="n">
         <f aca="false">B21+C20</f>
         <v>-28480.3125</v>
       </c>
-      <c r="D21" s="12" t="n">
+      <c r="D21" s="11" t="n">
         <f aca="false">C21+D20</f>
         <v>-48113.02109375</v>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="E21" s="11" t="n">
         <f aca="false">D21+E20</f>
         <v>-40972.8791738282</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="F21" s="11" t="n">
         <f aca="false">E21+F20</f>
         <v>-37662.3833511085</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="G21" s="11" t="n">
         <f aca="false">F21+G20</f>
         <v>-38286.848893264</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="H21" s="11" t="n">
         <f aca="false">G21+H20</f>
         <v>-254.487237828842</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="I21" s="11" t="n">
         <f aca="false">H21+I20</f>
         <v>33623.5143631308</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="J21" s="11" t="n">
         <f aca="false">I21+J20</f>
         <v>63232.9110081168</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="K21" s="11" t="n">
         <f aca="false">J21+K20</f>
         <v>88456.3160608399</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="L21" s="11" t="n">
         <f aca="false">K21+L20</f>
         <v>109173.114752513</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="M21" s="11" t="n">
         <f aca="false">L21+M20</f>
         <v>161859.375408207</v>
       </c>
-      <c r="N21" s="12" t="n">
+      <c r="N21" s="11" t="n">
         <f aca="false">M21+N20</f>
         <v>209787.758231932</v>
       </c>
-      <c r="O21" s="12" t="n">
+      <c r="O21" s="11" t="n">
         <f aca="false">N21+O20</f>
         <v>252827.42158331</v>
       </c>
-      <c r="P21" s="12" t="n">
+      <c r="P21" s="11" t="n">
         <f aca="false">O21+P20</f>
         <v>290843.925676851</v>
       </c>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="12" t="n">
+      <c r="B22" s="11" t="n">
         <f aca="false">B21+B17</f>
         <v>-12475</v>
       </c>
-      <c r="C22" s="12" t="n">
+      <c r="C22" s="11" t="n">
         <f aca="false">C21+C17</f>
-        <v>-22944.1195063306</v>
-      </c>
-      <c r="D22" s="12" t="n">
+        <v>-26688.1195063306</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <f aca="false">D21+D17</f>
-        <v>-21391.1642639564</v>
-      </c>
-      <c r="E22" s="12" t="n">
+        <v>-29815.164263956</v>
+      </c>
+      <c r="E22" s="11" t="n">
         <f aca="false">E21+E17</f>
-        <v>96391.5149731138</v>
-      </c>
-      <c r="F22" s="12" t="n">
+        <v>81415.5149731138</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <f aca="false">F21+F17</f>
-        <v>113514.715754352</v>
-      </c>
-      <c r="G22" s="12" t="n">
+        <v>94794.715754352</v>
+      </c>
+      <c r="G22" s="11" t="n">
         <f aca="false">G21+G17</f>
-        <v>123051.251734993</v>
-      </c>
-      <c r="H22" s="12" t="n">
+        <v>100587.251734994</v>
+      </c>
+      <c r="H22" s="11" t="n">
         <f aca="false">H21+H17</f>
-        <v>247240.596821044</v>
-      </c>
-      <c r="I22" s="12" t="n">
+        <v>221032.596821044</v>
+      </c>
+      <c r="I22" s="11" t="n">
         <f aca="false">I21+I17</f>
-        <v>377525.428938037</v>
-      </c>
-      <c r="J22" s="12" t="n">
+        <v>347573.428938037</v>
+      </c>
+      <c r="J22" s="11" t="n">
         <f aca="false">J21+J17</f>
-        <v>514149.361804062</v>
-      </c>
-      <c r="K22" s="12" t="n">
+        <v>480453.361804062</v>
+      </c>
+      <c r="K22" s="11" t="n">
         <f aca="false">K21+K17</f>
-        <v>585375.24594627</v>
-      </c>
-      <c r="L22" s="12" t="n">
+        <v>547935.24594627</v>
+      </c>
+      <c r="L22" s="11" t="n">
         <f aca="false">L21+L17</f>
-        <v>965376.699531582</v>
-      </c>
-      <c r="M22" s="12" t="n">
+        <v>924192.699531582</v>
+      </c>
+      <c r="M22" s="11" t="n">
         <f aca="false">M21+M17</f>
-        <v>1196012.54313073</v>
-      </c>
-      <c r="N22" s="12" t="n">
+        <v>1151084.54313073</v>
+      </c>
+      <c r="N22" s="11" t="n">
         <f aca="false">N21+N17</f>
-        <v>1436168.42211359</v>
-      </c>
-      <c r="O22" s="12" t="n">
+        <v>1387496.42211359</v>
+      </c>
+      <c r="O22" s="11" t="n">
         <f aca="false">O21+O17</f>
-        <v>1600093.51720044</v>
-      </c>
-      <c r="P22" s="12" t="n">
+        <v>1547677.51720044</v>
+      </c>
+      <c r="P22" s="11" t="n">
         <f aca="false">P21+P17</f>
-        <v>1759125.08255656</v>
-      </c>
-      <c r="Q22" s="3"/>
-      <c r="R22" s="7" t="s">
+        <v>1702965.08255656</v>
+      </c>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B23" s="20" t="str">
+      <c r="B23" s="19" t="str">
         <f aca="false">IF(B22&gt;0,"AHEAD","behind")</f>
         <v>behind</v>
       </c>
-      <c r="C23" s="20" t="str">
+      <c r="C23" s="19" t="str">
         <f aca="false">IF(C22&gt;0,"AHEAD","behind")</f>
         <v>behind</v>
       </c>
-      <c r="D23" s="20" t="str">
+      <c r="D23" s="19" t="str">
         <f aca="false">IF(D22&gt;0,"AHEAD","behind")</f>
         <v>behind</v>
       </c>
-      <c r="E23" s="20" t="str">
+      <c r="E23" s="19" t="str">
         <f aca="false">IF(E22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="F23" s="20" t="str">
+      <c r="F23" s="19" t="str">
         <f aca="false">IF(F22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="G23" s="20" t="str">
+      <c r="G23" s="19" t="str">
         <f aca="false">IF(G22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="H23" s="20" t="str">
+      <c r="H23" s="19" t="str">
         <f aca="false">IF(H22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="I23" s="20" t="str">
+      <c r="I23" s="19" t="str">
         <f aca="false">IF(I22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="J23" s="20" t="str">
+      <c r="J23" s="19" t="str">
         <f aca="false">IF(J22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="K23" s="20" t="str">
+      <c r="K23" s="19" t="str">
         <f aca="false">IF(K22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="L23" s="20" t="str">
+      <c r="L23" s="19" t="str">
         <f aca="false">IF(L22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="M23" s="20" t="str">
+      <c r="M23" s="19" t="str">
         <f aca="false">IF(M22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="N23" s="20" t="str">
+      <c r="N23" s="19" t="str">
         <f aca="false">IF(N22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="O23" s="20" t="str">
+      <c r="O23" s="19" t="str">
         <f aca="false">IF(O22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="P23" s="20" t="str">
+      <c r="P23" s="19" t="str">
         <f aca="false">IF(P22&gt;0,"AHEAD","behind")</f>
         <v>AHEAD</v>
       </c>
-      <c r="Q23" s="3"/>
-      <c r="R23" s="3"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -2458,484 +2454,484 @@
   <dimension ref="A1:R12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3"/>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="A5" s="2"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="11" t="n">
+      <c r="B6" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="11" t="n">
+      <c r="C6" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D6" s="11" t="n">
+      <c r="D6" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="L6" s="11" t="n">
+      <c r="L6" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="10" t="s">
+      <c r="Q6" s="2"/>
+      <c r="R6" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="12" t="n">
+      <c r="B7" s="11" t="n">
         <v>1107883.476</v>
       </c>
-      <c r="C7" s="12" t="n">
+      <c r="C7" s="11" t="n">
         <v>1130224.27392</v>
       </c>
-      <c r="D7" s="12" t="n">
+      <c r="D7" s="11" t="n">
         <v>1470581.13731659</v>
       </c>
-      <c r="E7" s="12" t="n">
+      <c r="E7" s="11" t="n">
         <v>2128361.5241759</v>
       </c>
-      <c r="F7" s="12" t="n">
+      <c r="F7" s="11" t="n">
         <v>2531696.60117519</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>2960567.60023987</v>
       </c>
-      <c r="H7" s="12" t="n">
+      <c r="H7" s="11" t="n">
         <v>3415973.30476096</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="11" t="n">
         <v>3898958.3702101</v>
       </c>
-      <c r="J7" s="12" t="n">
+      <c r="J7" s="11" t="n">
         <v>4410614.70976327</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="11" t="n">
         <v>4952082.94628947</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="11" t="n">
         <v>5524553.93215493</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="11" t="n">
         <v>6129270.33838766</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="11" t="n">
         <v>6767528.314843</v>
       </c>
-      <c r="O7" s="12" t="n">
+      <c r="O7" s="11" t="n">
         <v>7045784.99129078</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="11" t="n">
         <v>7328447.27269707</v>
       </c>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B8" s="22" t="n">
+      <c r="B8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="22" t="n">
+      <c r="D8" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="E8" s="22" t="n">
+      <c r="E8" s="21" t="n">
         <v>3.5</v>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="21" t="n">
         <v>4.5</v>
       </c>
-      <c r="H8" s="22" t="n">
+      <c r="H8" s="21" t="n">
         <v>5</v>
       </c>
-      <c r="I8" s="22" t="n">
+      <c r="I8" s="21" t="n">
         <v>5.5</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="21" t="n">
         <v>6</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="21" t="n">
         <v>6.5</v>
       </c>
-      <c r="L8" s="22" t="n">
+      <c r="L8" s="21" t="n">
         <v>7</v>
       </c>
-      <c r="M8" s="22" t="n">
+      <c r="M8" s="21" t="n">
         <v>7.5</v>
       </c>
-      <c r="N8" s="22" t="n">
+      <c r="N8" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="O8" s="22" t="n">
+      <c r="O8" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="P8" s="22" t="n">
+      <c r="P8" s="21" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B9" s="20" t="n">
+      <c r="B9" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="C9" s="20" t="n">
+      <c r="C9" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="D9" s="20" t="n">
+      <c r="D9" s="19" t="n">
         <v>12</v>
       </c>
-      <c r="E9" s="20" t="n">
+      <c r="E9" s="19" t="n">
         <v>16</v>
       </c>
-      <c r="F9" s="20" t="n">
+      <c r="F9" s="19" t="n">
         <v>19</v>
       </c>
-      <c r="G9" s="20" t="n">
+      <c r="G9" s="19" t="n">
         <v>23</v>
       </c>
-      <c r="H9" s="20" t="n">
+      <c r="H9" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="I9" s="20" t="n">
+      <c r="I9" s="19" t="n">
         <v>27</v>
       </c>
-      <c r="J9" s="20" t="n">
+      <c r="J9" s="19" t="n">
         <v>28</v>
       </c>
-      <c r="K9" s="20" t="n">
+      <c r="K9" s="19" t="n">
         <v>32</v>
       </c>
-      <c r="L9" s="20" t="n">
+      <c r="L9" s="19" t="n">
         <v>33</v>
       </c>
-      <c r="M9" s="20" t="n">
+      <c r="M9" s="19" t="n">
         <v>36</v>
       </c>
-      <c r="N9" s="20" t="n">
+      <c r="N9" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="O9" s="20" t="n">
+      <c r="O9" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="P9" s="20" t="n">
+      <c r="P9" s="19" t="n">
         <v>37</v>
       </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>314146.07309104</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <v>303726.24221904</v>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>361218.979335931</v>
       </c>
-      <c r="E10" s="12" t="n">
+      <c r="E10" s="11" t="n">
         <v>487332.012318055</v>
       </c>
-      <c r="F10" s="12" t="n">
+      <c r="F10" s="11" t="n">
         <v>479969.659557169</v>
       </c>
-      <c r="G10" s="12" t="n">
+      <c r="G10" s="11" t="n">
         <v>466088.769207364</v>
       </c>
-      <c r="H10" s="12" t="n">
+      <c r="H10" s="11" t="n">
         <v>597197.758851492</v>
       </c>
-      <c r="I10" s="12" t="n">
+      <c r="I10" s="11" t="n">
         <v>735647.486330165</v>
       </c>
-      <c r="J10" s="12" t="n">
+      <c r="J10" s="11" t="n">
         <v>881486.5874483</v>
       </c>
-      <c r="K10" s="12" t="n">
+      <c r="K10" s="11" t="n">
         <v>898428.470548401</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="11" t="n">
         <v>1062695.91705148</v>
       </c>
-      <c r="M10" s="12" t="n">
+      <c r="M10" s="11" t="n">
         <v>1234746.42040954</v>
       </c>
-      <c r="N10" s="12" t="n">
+      <c r="N10" s="11" t="n">
         <v>1414609.86275326</v>
       </c>
-      <c r="O10" s="12" t="n">
+      <c r="O10" s="11" t="n">
         <v>1480797.94885832</v>
       </c>
-      <c r="P10" s="12" t="n">
+      <c r="P10" s="11" t="n">
         <v>1544843.49387317</v>
       </c>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="7" t="s">
+      <c r="Q10" s="2"/>
+      <c r="R10" s="6" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B11" s="13" t="n">
-        <v>94158.4292364159</v>
-      </c>
-      <c r="C11" s="13" t="n">
-        <v>186848.926124032</v>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>288686.517858404</v>
-      </c>
-      <c r="E11" s="13" t="n">
-        <v>427119.322785626</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>576457.186608494</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <v>720242.694291439</v>
-      </c>
-      <c r="H11" s="13" t="n">
-        <v>916471.797832036</v>
-      </c>
-      <c r="I11" s="13" t="n">
-        <v>1168080.7923641</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>1478025.42734342</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>1794746.81556278</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>2177175.18238338</v>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>2628423.75054719</v>
-      </c>
-      <c r="N11" s="13" t="n">
-        <v>3151617.69564849</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>3715136.87519182</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>4304274.27274109</v>
-      </c>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
+      <c r="B11" s="12" t="n">
+        <v>62958.4292364159</v>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>124448.926124032</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>195086.517858404</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>302319.322785626</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>420457.186608494</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>533042.694291439</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>698071.797832036</v>
+      </c>
+      <c r="I11" s="12" t="n">
+        <v>918480.792364102</v>
+      </c>
+      <c r="J11" s="12" t="n">
+        <v>1197225.42734342</v>
+      </c>
+      <c r="K11" s="12" t="n">
+        <v>1482746.81556278</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>1833975.18238338</v>
+      </c>
+      <c r="M11" s="12" t="n">
+        <v>2254023.75054719</v>
+      </c>
+      <c r="N11" s="12" t="n">
+        <v>2746017.69564849</v>
+      </c>
+      <c r="O11" s="12" t="n">
+        <v>3278336.87519182</v>
+      </c>
+      <c r="P11" s="12" t="n">
+        <v>3836274.27274109</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>722514.397345807</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>814784.283227823</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>1019423.92033104</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>1867217.68455785</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>1982323.55921217</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>2066998.57190214</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>2784973.43382394</v>
-      </c>
-      <c r="I12" s="12" t="n">
-        <v>3588363.68812422</v>
-      </c>
-      <c r="J12" s="12" t="n">
-        <v>4480151.48996621</v>
-      </c>
-      <c r="K12" s="12" t="n">
-        <v>4863505.48237858</v>
-      </c>
-      <c r="L12" s="12" t="n">
-        <v>7857544.27315891</v>
-      </c>
-      <c r="M12" s="12" t="n">
-        <v>9340457.46435439</v>
-      </c>
-      <c r="N12" s="12" t="n">
-        <v>10942353.2656805</v>
-      </c>
-      <c r="O12" s="12" t="n">
-        <v>11949731.8634761</v>
-      </c>
-      <c r="P12" s="12" t="n">
-        <v>12958190.7073309</v>
-      </c>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="7" t="s">
+      <c r="B12" s="11" t="n">
+        <v>691314.397345807</v>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>752384.283227823</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>925823.920331045</v>
+      </c>
+      <c r="E12" s="11" t="n">
+        <v>1742417.68455785</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>1826323.55921217</v>
+      </c>
+      <c r="G12" s="11" t="n">
+        <v>1879798.57190215</v>
+      </c>
+      <c r="H12" s="11" t="n">
+        <v>2566573.43382394</v>
+      </c>
+      <c r="I12" s="11" t="n">
+        <v>3338763.68812422</v>
+      </c>
+      <c r="J12" s="11" t="n">
+        <v>4199351.48996621</v>
+      </c>
+      <c r="K12" s="11" t="n">
+        <v>4551505.48237858</v>
+      </c>
+      <c r="L12" s="11" t="n">
+        <v>7514344.27315891</v>
+      </c>
+      <c r="M12" s="11" t="n">
+        <v>8966057.46435439</v>
+      </c>
+      <c r="N12" s="11" t="n">
+        <v>10536753.2656805</v>
+      </c>
+      <c r="O12" s="11" t="n">
+        <v>11512931.8634761</v>
+      </c>
+      <c r="P12" s="11" t="n">
+        <v>12490190.7073309</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="6" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2959,1062 +2955,1062 @@
   <dimension ref="A1:R27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="2" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="62"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="8" t="n">
+      <c r="B4" s="7" t="n">
         <v>0.2</v>
       </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="21" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B5" s="8" t="n">
+      <c r="B5" s="7" t="n">
         <v>0.0875</v>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="21" t="s">
+      <c r="C5" s="2"/>
+      <c r="D5" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
-      <c r="P6" s="3"/>
-      <c r="Q6" s="3"/>
-      <c r="R6" s="3"/>
+      <c r="A6" s="2"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="3"/>
-      <c r="O7" s="3"/>
-      <c r="P7" s="3"/>
-      <c r="Q7" s="3"/>
-      <c r="R7" s="3"/>
+      <c r="A7" s="2"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="11" t="n">
+      <c r="B8" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="C8" s="11" t="n">
+      <c r="C8" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="11" t="n">
+      <c r="D8" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="E8" s="11" t="n">
+      <c r="E8" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="11" t="n">
+      <c r="F8" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="11" t="n">
+      <c r="G8" s="10" t="n">
         <v>6</v>
       </c>
-      <c r="H8" s="11" t="n">
+      <c r="H8" s="10" t="n">
         <v>7</v>
       </c>
-      <c r="I8" s="11" t="n">
+      <c r="I8" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="10" t="n">
         <v>9</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="L8" s="11" t="n">
+      <c r="L8" s="10" t="n">
         <v>11</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="M8" s="10" t="n">
         <v>12</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="N8" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="O8" s="11" t="n">
+      <c r="O8" s="10" t="n">
         <v>14</v>
       </c>
-      <c r="P8" s="11" t="n">
+      <c r="P8" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="10" t="s">
+      <c r="Q8" s="2"/>
+      <c r="R8" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B9" s="12" t="n">
+      <c r="B9" s="11" t="n">
         <f aca="false">'Year by year'!B17</f>
         <v>0</v>
       </c>
-      <c r="C9" s="12" t="n">
+      <c r="C9" s="11" t="n">
         <f aca="false">'Year by year'!C17</f>
-        <v>5536.19299366938</v>
-      </c>
-      <c r="D9" s="12" t="n">
+        <v>1792.19299366938</v>
+      </c>
+      <c r="D9" s="11" t="n">
         <f aca="false">'Year by year'!D17</f>
-        <v>26721.8568297936</v>
-      </c>
-      <c r="E9" s="12" t="n">
+        <v>18297.8568297941</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <f aca="false">'Year by year'!E17</f>
-        <v>137364.394146942</v>
-      </c>
-      <c r="F9" s="12" t="n">
+        <v>122388.394146942</v>
+      </c>
+      <c r="F9" s="11" t="n">
         <f aca="false">'Year by year'!F17</f>
-        <v>151177.09910546</v>
-      </c>
-      <c r="G9" s="12" t="n">
+        <v>132457.09910546</v>
+      </c>
+      <c r="G9" s="11" t="n">
         <f aca="false">'Year by year'!G17</f>
-        <v>161338.100628257</v>
-      </c>
-      <c r="H9" s="12" t="n">
+        <v>138874.100628258</v>
+      </c>
+      <c r="H9" s="11" t="n">
         <f aca="false">'Year by year'!H17</f>
-        <v>247495.084058873</v>
-      </c>
-      <c r="I9" s="12" t="n">
+        <v>221287.084058873</v>
+      </c>
+      <c r="I9" s="11" t="n">
         <f aca="false">'Year by year'!I17</f>
-        <v>343901.914574906</v>
-      </c>
-      <c r="J9" s="12" t="n">
+        <v>313949.914574906</v>
+      </c>
+      <c r="J9" s="11" t="n">
         <f aca="false">'Year by year'!J17</f>
-        <v>450916.450795945</v>
-      </c>
-      <c r="K9" s="12" t="n">
+        <v>417220.450795945</v>
+      </c>
+      <c r="K9" s="11" t="n">
         <f aca="false">'Year by year'!K17</f>
-        <v>496918.92988543</v>
-      </c>
-      <c r="L9" s="12" t="n">
+        <v>459478.92988543</v>
+      </c>
+      <c r="L9" s="11" t="n">
         <f aca="false">'Year by year'!L17</f>
-        <v>856203.584779069</v>
-      </c>
-      <c r="M9" s="12" t="n">
+        <v>815019.584779069</v>
+      </c>
+      <c r="M9" s="11" t="n">
         <f aca="false">'Year by year'!M17</f>
-        <v>1034153.16772253</v>
-      </c>
-      <c r="N9" s="12" t="n">
+        <v>989225.167722527</v>
+      </c>
+      <c r="N9" s="11" t="n">
         <f aca="false">'Year by year'!N17</f>
-        <v>1226380.66388166</v>
-      </c>
-      <c r="O9" s="12" t="n">
+        <v>1177708.66388166</v>
+      </c>
+      <c r="O9" s="11" t="n">
         <f aca="false">'Year by year'!O17</f>
-        <v>1347266.09561713</v>
-      </c>
-      <c r="P9" s="12" t="n">
+        <v>1294850.09561713</v>
+      </c>
+      <c r="P9" s="11" t="n">
         <f aca="false">'Year by year'!P17</f>
-        <v>1468281.15687971</v>
-      </c>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="7" t="s">
+        <v>1412121.15687971</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="6" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <f aca="false">B9*(1-$B$4)</f>
         <v>0</v>
       </c>
-      <c r="C10" s="12" t="n">
+      <c r="C10" s="11" t="n">
         <f aca="false">C9*(1-$B$4)</f>
-        <v>4428.9543949355</v>
-      </c>
-      <c r="D10" s="12" t="n">
+        <v>1433.7543949355</v>
+      </c>
+      <c r="D10" s="11" t="n">
         <f aca="false">D9*(1-$B$4)</f>
-        <v>21377.4854638349</v>
-      </c>
-      <c r="E10" s="12" t="n">
+        <v>14638.2854638352</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <f aca="false">E9*(1-$B$4)</f>
-        <v>109891.515317554</v>
-      </c>
-      <c r="F10" s="12" t="n">
+        <v>97910.7153175536</v>
+      </c>
+      <c r="F10" s="11" t="n">
         <f aca="false">F9*(1-$B$4)</f>
-        <v>120941.679284368</v>
-      </c>
-      <c r="G10" s="12" t="n">
+        <v>105965.679284368</v>
+      </c>
+      <c r="G10" s="11" t="n">
         <f aca="false">G9*(1-$B$4)</f>
-        <v>129070.480502605</v>
-      </c>
-      <c r="H10" s="12" t="n">
+        <v>111099.280502606</v>
+      </c>
+      <c r="H10" s="11" t="n">
         <f aca="false">H9*(1-$B$4)</f>
-        <v>197996.067247098</v>
-      </c>
-      <c r="I10" s="12" t="n">
+        <v>177029.667247098</v>
+      </c>
+      <c r="I10" s="11" t="n">
         <f aca="false">I9*(1-$B$4)</f>
-        <v>275121.531659925</v>
-      </c>
-      <c r="J10" s="12" t="n">
+        <v>251159.931659925</v>
+      </c>
+      <c r="J10" s="11" t="n">
         <f aca="false">J9*(1-$B$4)</f>
-        <v>360733.160636756</v>
-      </c>
-      <c r="K10" s="12" t="n">
+        <v>333776.360636756</v>
+      </c>
+      <c r="K10" s="11" t="n">
         <f aca="false">K9*(1-$B$4)</f>
-        <v>397535.143908344</v>
-      </c>
-      <c r="L10" s="12" t="n">
+        <v>367583.143908344</v>
+      </c>
+      <c r="L10" s="11" t="n">
         <f aca="false">L9*(1-$B$4)</f>
-        <v>684962.867823255</v>
-      </c>
-      <c r="M10" s="12" t="n">
+        <v>652015.667823255</v>
+      </c>
+      <c r="M10" s="11" t="n">
         <f aca="false">M9*(1-$B$4)</f>
-        <v>827322.534178021</v>
-      </c>
-      <c r="N10" s="12" t="n">
+        <v>791380.134178022</v>
+      </c>
+      <c r="N10" s="11" t="n">
         <f aca="false">N9*(1-$B$4)</f>
-        <v>981104.531105328</v>
-      </c>
-      <c r="O10" s="12" t="n">
+        <v>942166.931105328</v>
+      </c>
+      <c r="O10" s="11" t="n">
         <f aca="false">O9*(1-$B$4)</f>
-        <v>1077812.87649371</v>
-      </c>
-      <c r="P10" s="12" t="n">
+        <v>1035880.07649371</v>
+      </c>
+      <c r="P10" s="11" t="n">
         <f aca="false">P9*(1-$B$4)</f>
-        <v>1174624.92550377</v>
-      </c>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
+        <v>1129696.92550377</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="12" t="n">
         <f aca="false">B10</f>
         <v>0</v>
       </c>
-      <c r="C11" s="13" t="n">
+      <c r="C11" s="12" t="n">
         <f aca="false">C10</f>
-        <v>4428.9543949355</v>
-      </c>
-      <c r="D11" s="13" t="n">
+        <v>1433.7543949355</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <f aca="false">D10</f>
-        <v>21377.4854638349</v>
-      </c>
-      <c r="E11" s="13" t="n">
+        <v>14638.2854638352</v>
+      </c>
+      <c r="E11" s="12" t="n">
         <f aca="false">E10</f>
-        <v>109891.515317554</v>
-      </c>
-      <c r="F11" s="13" t="n">
+        <v>97910.7153175536</v>
+      </c>
+      <c r="F11" s="12" t="n">
         <f aca="false">F10</f>
-        <v>120941.679284368</v>
-      </c>
-      <c r="G11" s="13" t="n">
+        <v>105965.679284368</v>
+      </c>
+      <c r="G11" s="12" t="n">
         <f aca="false">G10</f>
-        <v>129070.480502605</v>
-      </c>
-      <c r="H11" s="13" t="n">
+        <v>111099.280502606</v>
+      </c>
+      <c r="H11" s="12" t="n">
         <f aca="false">H10</f>
-        <v>197996.067247098</v>
-      </c>
-      <c r="I11" s="13" t="n">
+        <v>177029.667247098</v>
+      </c>
+      <c r="I11" s="12" t="n">
         <f aca="false">I10</f>
-        <v>275121.531659925</v>
-      </c>
-      <c r="J11" s="13" t="n">
+        <v>251159.931659925</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <f aca="false">J10</f>
-        <v>360733.160636756</v>
-      </c>
-      <c r="K11" s="13" t="n">
+        <v>333776.360636756</v>
+      </c>
+      <c r="K11" s="12" t="n">
         <f aca="false">K10</f>
-        <v>397535.143908344</v>
-      </c>
-      <c r="L11" s="13" t="n">
+        <v>367583.143908344</v>
+      </c>
+      <c r="L11" s="12" t="n">
         <f aca="false">L10</f>
-        <v>684962.867823255</v>
-      </c>
-      <c r="M11" s="13" t="n">
+        <v>652015.667823255</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <f aca="false">M10</f>
-        <v>827322.534178021</v>
-      </c>
-      <c r="N11" s="13" t="n">
+        <v>791380.134178022</v>
+      </c>
+      <c r="N11" s="12" t="n">
         <f aca="false">N10</f>
-        <v>981104.531105328</v>
-      </c>
-      <c r="O11" s="13" t="n">
+        <v>942166.931105328</v>
+      </c>
+      <c r="O11" s="12" t="n">
         <f aca="false">O10</f>
-        <v>1077812.87649371</v>
-      </c>
-      <c r="P11" s="13" t="n">
+        <v>1035880.07649371</v>
+      </c>
+      <c r="P11" s="12" t="n">
         <f aca="false">P10</f>
-        <v>1174624.92550377</v>
-      </c>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
+        <v>1129696.92550377</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,36,-B10))</f>
         <v>0</v>
       </c>
-      <c r="C12" s="13" t="n">
+      <c r="C12" s="12" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,36,-C10))</f>
-        <v>140.324808552673</v>
-      </c>
-      <c r="D12" s="13" t="n">
+        <v>45.4263677248379</v>
+      </c>
+      <c r="D12" s="12" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,36,-D10))</f>
-        <v>677.313715056633</v>
-      </c>
-      <c r="E12" s="13" t="n">
+        <v>463.792223194017</v>
+      </c>
+      <c r="E12" s="12" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,36,-E10))</f>
-        <v>3481.74861907183</v>
-      </c>
-      <c r="F12" s="13" t="n">
+        <v>3102.15485576049</v>
+      </c>
+      <c r="F12" s="12" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,36,-F10))</f>
-        <v>3831.85656890578</v>
-      </c>
-      <c r="G12" s="13" t="n">
+        <v>3357.3643647666</v>
+      </c>
+      <c r="G12" s="12" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,36,-G10))</f>
-        <v>4089.4055010005</v>
-      </c>
-      <c r="H12" s="13" t="n">
+        <v>3520.01485603352</v>
+      </c>
+      <c r="H12" s="12" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,36,-H10))</f>
-        <v>6273.20982631968</v>
-      </c>
-      <c r="I12" s="13" t="n">
+        <v>5608.92074052484</v>
+      </c>
+      <c r="I12" s="12" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,36,-I10))</f>
-        <v>8716.81503495347</v>
-      </c>
-      <c r="J12" s="13" t="n">
+        <v>7957.62750833079</v>
+      </c>
+      <c r="J12" s="12" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,36,-J10))</f>
-        <v>11429.291699828</v>
-      </c>
-      <c r="K12" s="13" t="n">
+        <v>10575.2057323775</v>
+      </c>
+      <c r="K12" s="12" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,36,-K10))</f>
-        <v>12595.3076025543</v>
-      </c>
-      <c r="L12" s="13" t="n">
+        <v>11646.323194276</v>
+      </c>
+      <c r="L12" s="12" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,36,-L10))</f>
-        <v>21702.0259686796</v>
-      </c>
-      <c r="M12" s="13" t="n">
+        <v>20658.1431195734</v>
+      </c>
+      <c r="M12" s="12" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,36,-M10))</f>
-        <v>26212.479485586</v>
-      </c>
-      <c r="N12" s="13" t="n">
+        <v>25073.698195652</v>
+      </c>
+      <c r="N12" s="12" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,36,-N10))</f>
-        <v>31084.8324956662</v>
-      </c>
-      <c r="O12" s="13" t="n">
+        <v>29851.1527649043</v>
+      </c>
+      <c r="O12" s="12" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,36,-O10))</f>
-        <v>34148.8920550935</v>
-      </c>
-      <c r="P12" s="13" t="n">
+        <v>32820.3138835038</v>
+      </c>
+      <c r="P12" s="12" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,36,-P10))</f>
-        <v>37216.2373089673</v>
-      </c>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
+        <v>35792.7606965498</v>
+      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="B13" s="12" t="n">
+      <c r="B13" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,60,-B10))</f>
         <v>0</v>
       </c>
-      <c r="C13" s="12" t="n">
+      <c r="C13" s="11" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,60,-C10))</f>
-        <v>91.4013624967347</v>
-      </c>
-      <c r="D13" s="12" t="n">
+        <v>29.5887230928903</v>
+      </c>
+      <c r="D13" s="11" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,60,-D10))</f>
-        <v>441.172142206513</v>
-      </c>
-      <c r="E13" s="12" t="n">
+        <v>302.093703547871</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,60,-E10))</f>
-        <v>2267.85677412726</v>
-      </c>
-      <c r="F13" s="12" t="n">
+        <v>2020.60621651188</v>
+      </c>
+      <c r="F13" s="11" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,60,-F10))</f>
-        <v>2495.90157936033</v>
-      </c>
-      <c r="G13" s="12" t="n">
+        <v>2186.8383823411</v>
+      </c>
+      <c r="G13" s="11" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,60,-G10))</f>
-        <v>2663.65754172959</v>
-      </c>
-      <c r="H13" s="12" t="n">
+        <v>2292.78170530654</v>
+      </c>
+      <c r="H13" s="11" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,60,-H10))</f>
-        <v>4086.09091483847</v>
-      </c>
-      <c r="I13" s="12" t="n">
+        <v>3653.40243901156</v>
+      </c>
+      <c r="I13" s="11" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,60,-I10))</f>
-        <v>5677.74707155725</v>
-      </c>
-      <c r="J13" s="12" t="n">
+        <v>5183.2459563265</v>
+      </c>
+      <c r="J13" s="11" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,60,-J10))</f>
-        <v>7444.53418117283</v>
-      </c>
-      <c r="K13" s="12" t="n">
+        <v>6888.22042653823</v>
+      </c>
+      <c r="K13" s="11" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,60,-K10))</f>
-        <v>8204.02527402571</v>
-      </c>
-      <c r="L13" s="12" t="n">
+        <v>7585.89887998727</v>
+      </c>
+      <c r="L13" s="11" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,60,-L10))</f>
-        <v>14135.7380988855</v>
-      </c>
-      <c r="M13" s="12" t="n">
+        <v>13455.7990654432</v>
+      </c>
+      <c r="M13" s="11" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,60,-M10))</f>
-        <v>17073.647661532</v>
-      </c>
-      <c r="N13" s="12" t="n">
+        <v>16331.8959886859</v>
+      </c>
+      <c r="N13" s="11" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,60,-N10))</f>
-        <v>20247.2825182597</v>
-      </c>
-      <c r="O13" s="12" t="n">
+        <v>19443.7182060097</v>
+      </c>
+      <c r="O13" s="11" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,60,-O10))</f>
-        <v>22243.0751467433</v>
-      </c>
-      <c r="P13" s="12" t="n">
+        <v>21377.6981950895</v>
+      </c>
+      <c r="P13" s="11" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,60,-P10))</f>
-        <v>24241.0079310002</v>
-      </c>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="7" t="s">
+        <v>23313.8183399425</v>
+      </c>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="6" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="B14" s="13" t="n">
+      <c r="B14" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,84,-B10))</f>
         <v>0</v>
       </c>
-      <c r="C14" s="13" t="n">
+      <c r="C14" s="12" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,84,-C10))</f>
-        <v>70.6971504836004</v>
-      </c>
-      <c r="D14" s="13" t="n">
+        <v>22.886293507828</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,84,-D10))</f>
-        <v>341.23794738684</v>
-      </c>
-      <c r="E14" s="13" t="n">
+        <v>233.663519191358</v>
+      </c>
+      <c r="E14" s="12" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,84,-E10))</f>
-        <v>1754.14246851578</v>
-      </c>
-      <c r="F14" s="13" t="n">
+        <v>1562.89904061269</v>
+      </c>
+      <c r="F14" s="12" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,84,-F10))</f>
-        <v>1930.53062589299</v>
-      </c>
-      <c r="G14" s="13" t="n">
+        <v>1691.47634101413</v>
+      </c>
+      <c r="G14" s="12" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,84,-G10))</f>
-        <v>2060.28655285266</v>
-      </c>
-      <c r="H14" s="13" t="n">
+        <v>1773.42141099804</v>
+      </c>
+      <c r="H14" s="12" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,84,-H10))</f>
-        <v>3160.51070142776</v>
-      </c>
-      <c r="I14" s="13" t="n">
+        <v>2825.83470259736</v>
+      </c>
+      <c r="I14" s="12" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,84,-I10))</f>
-        <v>4391.62533425084</v>
-      </c>
-      <c r="J14" s="13" t="n">
+        <v>4009.13847844467</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,84,-J10))</f>
-        <v>5758.20030369334</v>
-      </c>
-      <c r="K14" s="13" t="n">
+        <v>5327.90259091139</v>
+      </c>
+      <c r="K14" s="12" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,84,-K10))</f>
-        <v>6345.65167876767</v>
-      </c>
-      <c r="L14" s="13" t="n">
+        <v>5867.54310900995</v>
+      </c>
+      <c r="L14" s="12" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,84,-L10))</f>
-        <v>10933.7145122905</v>
-      </c>
-      <c r="M14" s="13" t="n">
+        <v>10407.795085557</v>
+      </c>
+      <c r="M14" s="12" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,84,-M10))</f>
-        <v>13206.1295921538</v>
-      </c>
-      <c r="N14" s="13" t="n">
+        <v>12632.3993084445</v>
+      </c>
+      <c r="N14" s="12" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,84,-N10))</f>
-        <v>15660.8735359773</v>
-      </c>
-      <c r="O14" s="13" t="n">
+        <v>15039.3323952922</v>
+      </c>
+      <c r="O14" s="12" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,84,-O10))</f>
-        <v>17204.5797558382</v>
-      </c>
-      <c r="P14" s="13" t="n">
+        <v>16535.2277581773</v>
+      </c>
+      <c r="P14" s="12" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,84,-P10))</f>
-        <v>18749.941343963</v>
-      </c>
-      <c r="Q14" s="3"/>
-      <c r="R14" s="3"/>
+        <v>18032.7784893264</v>
+      </c>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="14" t="s">
+      <c r="A15" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15"/>
-      <c r="D15" s="15"/>
-      <c r="E15" s="15"/>
-      <c r="F15" s="15"/>
-      <c r="G15" s="15"/>
-      <c r="H15" s="15"/>
-      <c r="I15" s="15"/>
-      <c r="J15" s="15"/>
-      <c r="K15" s="15"/>
-      <c r="L15" s="15"/>
-      <c r="M15" s="15"/>
-      <c r="N15" s="15"/>
-      <c r="O15" s="15"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="3"/>
-      <c r="R15" s="15"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
+      <c r="O15" s="14"/>
+      <c r="P15" s="14"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="14"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="B16" s="13" t="n">
+      <c r="B16" s="12" t="n">
         <v>314146.07309104</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="12" t="n">
         <v>303726.24221904</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="12" t="n">
         <v>361218.979335931</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="12" t="n">
         <v>487332.012318055</v>
       </c>
-      <c r="F16" s="13" t="n">
+      <c r="F16" s="12" t="n">
         <v>479969.659557169</v>
       </c>
-      <c r="G16" s="13" t="n">
+      <c r="G16" s="12" t="n">
         <v>466088.769207364</v>
       </c>
-      <c r="H16" s="13" t="n">
+      <c r="H16" s="12" t="n">
         <v>597197.758851492</v>
       </c>
-      <c r="I16" s="13" t="n">
+      <c r="I16" s="12" t="n">
         <v>735647.486330165</v>
       </c>
-      <c r="J16" s="13" t="n">
+      <c r="J16" s="12" t="n">
         <v>881486.5874483</v>
       </c>
-      <c r="K16" s="13" t="n">
+      <c r="K16" s="12" t="n">
         <v>898428.470548401</v>
       </c>
-      <c r="L16" s="13" t="n">
+      <c r="L16" s="12" t="n">
         <v>1062695.91705148</v>
       </c>
-      <c r="M16" s="13" t="n">
+      <c r="M16" s="12" t="n">
         <v>1234746.42040954</v>
       </c>
-      <c r="N16" s="13" t="n">
+      <c r="N16" s="12" t="n">
         <v>1414609.86275326</v>
       </c>
-      <c r="O16" s="13" t="n">
+      <c r="O16" s="12" t="n">
         <v>1480797.94885832</v>
       </c>
-      <c r="P16" s="13" t="n">
+      <c r="P16" s="12" t="n">
         <v>1544843.49387317</v>
       </c>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B17" s="13" t="n">
-        <v>94158.4292364159</v>
-      </c>
-      <c r="C17" s="13" t="n">
-        <v>186848.926124032</v>
-      </c>
-      <c r="D17" s="13" t="n">
-        <v>288686.517858404</v>
-      </c>
-      <c r="E17" s="13" t="n">
-        <v>427119.322785626</v>
-      </c>
-      <c r="F17" s="13" t="n">
-        <v>576457.186608494</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <v>720242.694291439</v>
-      </c>
-      <c r="H17" s="13" t="n">
-        <v>916471.797832036</v>
-      </c>
-      <c r="I17" s="13" t="n">
-        <v>1168080.7923641</v>
-      </c>
-      <c r="J17" s="13" t="n">
-        <v>1478025.42734342</v>
-      </c>
-      <c r="K17" s="13" t="n">
-        <v>1794746.81556278</v>
-      </c>
-      <c r="L17" s="13" t="n">
-        <v>2177175.18238338</v>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>2628423.75054719</v>
-      </c>
-      <c r="N17" s="13" t="n">
-        <v>3151617.69564849</v>
-      </c>
-      <c r="O17" s="13" t="n">
-        <v>3715136.87519182</v>
-      </c>
-      <c r="P17" s="13" t="n">
-        <v>4304274.27274109</v>
-      </c>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
+      <c r="B17" s="12" t="n">
+        <v>62958.4292364159</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <v>124448.926124032</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <v>195086.517858404</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <v>302319.322785626</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>420457.186608494</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>533042.694291439</v>
+      </c>
+      <c r="H17" s="12" t="n">
+        <v>698071.797832036</v>
+      </c>
+      <c r="I17" s="12" t="n">
+        <v>918480.792364102</v>
+      </c>
+      <c r="J17" s="12" t="n">
+        <v>1197225.42734342</v>
+      </c>
+      <c r="K17" s="12" t="n">
+        <v>1482746.81556278</v>
+      </c>
+      <c r="L17" s="12" t="n">
+        <v>1833975.18238338</v>
+      </c>
+      <c r="M17" s="12" t="n">
+        <v>2254023.75054719</v>
+      </c>
+      <c r="N17" s="12" t="n">
+        <v>2746017.69564849</v>
+      </c>
+      <c r="O17" s="12" t="n">
+        <v>3278336.87519182</v>
+      </c>
+      <c r="P17" s="12" t="n">
+        <v>3836274.27274109</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="17" t="n">
+      <c r="B18" s="16" t="n">
         <f aca="false">IF(B16=0,0,B13*12/B16)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="17" t="n">
+      <c r="C18" s="16" t="n">
         <f aca="false">IF(C16=0,0,C13*12/C16)</f>
-        <v>0.00361120047430679</v>
-      </c>
-      <c r="D18" s="17" t="n">
+        <v>0.00116902864408608</v>
+      </c>
+      <c r="D18" s="16" t="n">
         <f aca="false">IF(D16=0,0,D13*12/D16)</f>
-        <v>0.0146561116921675</v>
-      </c>
-      <c r="E18" s="17" t="n">
+        <v>0.010035808332217</v>
+      </c>
+      <c r="E18" s="16" t="n">
         <f aca="false">IF(E16=0,0,E13*12/E16)</f>
-        <v>0.055843409834866</v>
-      </c>
-      <c r="F18" s="17" t="n">
+        <v>0.0497551443066657</v>
+      </c>
+      <c r="F18" s="16" t="n">
         <f aca="false">IF(F16=0,0,F13*12/F16)</f>
-        <v>0.0624014838353683</v>
-      </c>
-      <c r="G18" s="17" t="n">
+        <v>0.0546744154876472</v>
+      </c>
+      <c r="G18" s="16" t="n">
         <f aca="false">IF(G16=0,0,G13*12/G16)</f>
-        <v>0.0685789759644139</v>
-      </c>
-      <c r="H18" s="17" t="n">
+        <v>0.0590303441777156</v>
+      </c>
+      <c r="H18" s="16" t="n">
         <f aca="false">IF(H16=0,0,H13*12/H16)</f>
-        <v>0.0821052829675052</v>
-      </c>
-      <c r="I18" s="17" t="n">
+        <v>0.0734109072218418</v>
+      </c>
+      <c r="I18" s="16" t="n">
         <f aca="false">IF(I16=0,0,I13*12/I16)</f>
-        <v>0.0926163225250367</v>
-      </c>
-      <c r="J18" s="17" t="n">
+        <v>0.0845499408775286</v>
+      </c>
+      <c r="J18" s="16" t="n">
         <f aca="false">IF(J16=0,0,J13*12/J16)</f>
-        <v>0.101345172400951</v>
-      </c>
-      <c r="K18" s="17" t="n">
+        <v>0.0937718693573506</v>
+      </c>
+      <c r="K18" s="16" t="n">
         <f aca="false">IF(K16=0,0,K13*12/K16)</f>
-        <v>0.10957834320212</v>
-      </c>
-      <c r="L18" s="17" t="n">
+        <v>0.101322241607372</v>
+      </c>
+      <c r="L18" s="16" t="n">
         <f aca="false">IF(L16=0,0,L13*12/L16)</f>
-        <v>0.159621256151311</v>
-      </c>
-      <c r="M18" s="17" t="n">
+        <v>0.151943360461313</v>
+      </c>
+      <c r="M18" s="16" t="n">
         <f aca="false">IF(M16=0,0,M13*12/M16)</f>
-        <v>0.165931861434697</v>
-      </c>
-      <c r="N18" s="17" t="n">
+        <v>0.158723077568613</v>
+      </c>
+      <c r="N18" s="16" t="n">
         <f aca="false">IF(N16=0,0,N13*12/N16)</f>
-        <v>0.171755758684043</v>
-      </c>
-      <c r="O18" s="17" t="n">
+        <v>0.164939199574076</v>
+      </c>
+      <c r="O18" s="16" t="n">
         <f aca="false">IF(O16=0,0,O13*12/O16)</f>
-        <v>0.180252074205471</v>
-      </c>
-      <c r="P18" s="17" t="n">
+        <v>0.17323928530483</v>
+      </c>
+      <c r="P18" s="16" t="n">
         <f aca="false">IF(P16=0,0,P13*12/P16)</f>
-        <v>0.188298747624388</v>
-      </c>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="7" t="s">
+        <v>0.181096545500472</v>
+      </c>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="6" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="20" t="str">
+      <c r="B19" s="19" t="str">
         <f aca="false">IF(B10=0,"-",IF(B17&gt;=B10,"yes","no - needs a note"))</f>
         <v>-</v>
       </c>
-      <c r="C19" s="20" t="str">
+      <c r="C19" s="19" t="str">
         <f aca="false">IF(C10=0,"-",IF(C17&gt;=C10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="D19" s="20" t="str">
+      <c r="D19" s="19" t="str">
         <f aca="false">IF(D10=0,"-",IF(D17&gt;=D10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="E19" s="20" t="str">
+      <c r="E19" s="19" t="str">
         <f aca="false">IF(E10=0,"-",IF(E17&gt;=E10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="F19" s="20" t="str">
+      <c r="F19" s="19" t="str">
         <f aca="false">IF(F10=0,"-",IF(F17&gt;=F10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="G19" s="20" t="str">
+      <c r="G19" s="19" t="str">
         <f aca="false">IF(G10=0,"-",IF(G17&gt;=G10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="H19" s="20" t="str">
+      <c r="H19" s="19" t="str">
         <f aca="false">IF(H10=0,"-",IF(H17&gt;=H10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="I19" s="20" t="str">
+      <c r="I19" s="19" t="str">
         <f aca="false">IF(I10=0,"-",IF(I17&gt;=I10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="J19" s="20" t="str">
+      <c r="J19" s="19" t="str">
         <f aca="false">IF(J10=0,"-",IF(J17&gt;=J10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="K19" s="20" t="str">
+      <c r="K19" s="19" t="str">
         <f aca="false">IF(K10=0,"-",IF(K17&gt;=K10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="L19" s="20" t="str">
+      <c r="L19" s="19" t="str">
         <f aca="false">IF(L10=0,"-",IF(L17&gt;=L10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="M19" s="20" t="str">
+      <c r="M19" s="19" t="str">
         <f aca="false">IF(M10=0,"-",IF(M17&gt;=M10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="N19" s="20" t="str">
+      <c r="N19" s="19" t="str">
         <f aca="false">IF(N10=0,"-",IF(N17&gt;=N10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="O19" s="20" t="str">
+      <c r="O19" s="19" t="str">
         <f aca="false">IF(O10=0,"-",IF(O17&gt;=O10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="P19" s="20" t="str">
+      <c r="P19" s="19" t="str">
         <f aca="false">IF(P10=0,"-",IF(P17&gt;=P10,"yes","no - needs a note"))</f>
         <v>yes</v>
       </c>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="3"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+      <c r="A21" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
-      <c r="J21" s="19"/>
-      <c r="K21" s="19"/>
-      <c r="L21" s="19"/>
-      <c r="M21" s="19"/>
-      <c r="N21" s="19"/>
-      <c r="O21" s="19"/>
-      <c r="P21" s="19"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="19"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+      <c r="M21" s="18"/>
+      <c r="N21" s="18"/>
+      <c r="O21" s="18"/>
+      <c r="P21" s="18"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>80</v>
       </c>
-      <c r="B22" s="23"/>
-      <c r="C22" s="23"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="23"/>
-      <c r="J22" s="23"/>
-      <c r="K22" s="23"/>
-      <c r="L22" s="23"/>
-      <c r="M22" s="23"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="23"/>
-      <c r="P22" s="23"/>
-      <c r="Q22" s="23"/>
-      <c r="R22" s="23"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="22"/>
+      <c r="O22" s="22"/>
+      <c r="P22" s="22"/>
+      <c r="Q22" s="22"/>
+      <c r="R22" s="22"/>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="B23" s="23"/>
-      <c r="C23" s="23"/>
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="F23" s="23"/>
-      <c r="G23" s="23"/>
-      <c r="H23" s="23"/>
-      <c r="I23" s="23"/>
-      <c r="J23" s="23"/>
-      <c r="K23" s="23"/>
-      <c r="L23" s="23"/>
-      <c r="M23" s="23"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="23"/>
-      <c r="P23" s="23"/>
-      <c r="Q23" s="23"/>
-      <c r="R23" s="23"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="22"/>
+      <c r="N23" s="22"/>
+      <c r="O23" s="22"/>
+      <c r="P23" s="22"/>
+      <c r="Q23" s="22"/>
+      <c r="R23" s="22"/>
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="23" t="s">
+      <c r="A24" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="B24" s="23"/>
-      <c r="C24" s="23"/>
-      <c r="D24" s="23"/>
-      <c r="E24" s="23"/>
-      <c r="F24" s="23"/>
-      <c r="G24" s="23"/>
-      <c r="H24" s="23"/>
-      <c r="I24" s="23"/>
-      <c r="J24" s="23"/>
-      <c r="K24" s="23"/>
-      <c r="L24" s="23"/>
-      <c r="M24" s="23"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="23"/>
-      <c r="P24" s="23"/>
-      <c r="Q24" s="23"/>
-      <c r="R24" s="23"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="22"/>
+      <c r="O24" s="22"/>
+      <c r="P24" s="22"/>
+      <c r="Q24" s="22"/>
+      <c r="R24" s="22"/>
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="23" t="s">
+      <c r="A25" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="B25" s="23"/>
-      <c r="C25" s="23"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
-      <c r="F25" s="23"/>
-      <c r="G25" s="23"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="23"/>
-      <c r="J25" s="23"/>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="23"/>
-      <c r="N25" s="23"/>
-      <c r="O25" s="23"/>
-      <c r="P25" s="23"/>
-      <c r="Q25" s="23"/>
-      <c r="R25" s="23"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22"/>
+      <c r="Q25" s="22"/>
+      <c r="R25" s="22"/>
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="23"/>
-      <c r="C26" s="23"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
-      <c r="F26" s="23"/>
-      <c r="G26" s="23"/>
-      <c r="H26" s="23"/>
-      <c r="I26" s="23"/>
-      <c r="J26" s="23"/>
-      <c r="K26" s="23"/>
-      <c r="L26" s="23"/>
-      <c r="M26" s="23"/>
-      <c r="N26" s="23"/>
-      <c r="O26" s="23"/>
-      <c r="P26" s="23"/>
-      <c r="Q26" s="23"/>
-      <c r="R26" s="23"/>
+      <c r="B26" s="22"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="22"/>
+      <c r="E26" s="22"/>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22"/>
+      <c r="Q26" s="22"/>
+      <c r="R26" s="22"/>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="F27" s="23"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="23"/>
-      <c r="J27" s="23"/>
-      <c r="K27" s="23"/>
-      <c r="L27" s="23"/>
-      <c r="M27" s="23"/>
-      <c r="N27" s="23"/>
-      <c r="O27" s="23"/>
-      <c r="P27" s="23"/>
-      <c r="Q27" s="23"/>
-      <c r="R27" s="23"/>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
+      <c r="N27" s="22"/>
+      <c r="O27" s="22"/>
+      <c r="P27" s="22"/>
+      <c r="Q27" s="22"/>
+      <c r="R27" s="22"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -4044,371 +4040,371 @@
   <dimension ref="A1:C41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3"/>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+      <c r="A4" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C5" s="24" t="s">
+      <c r="C5" s="23" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="24" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="25" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="25" t="s">
+      <c r="A7" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="25" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="25" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="25" t="s">
+      <c r="A9" s="24" t="s">
         <v>101</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="25" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="24" t="s">
         <v>104</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="25" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
+      <c r="A11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="26" t="s">
         <v>107</v>
       </c>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="24" t="s">
+      <c r="A13" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="23" t="s">
         <v>90</v>
       </c>
-      <c r="C13" s="24" t="s">
+      <c r="C13" s="23" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="24" t="s">
         <v>108</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="25" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="25" t="s">
+      <c r="A15" s="24" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="25" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="25" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="25" t="s">
+      <c r="A16" s="24" t="s">
         <v>114</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="25" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="25" t="s">
+      <c r="A17" s="24" t="s">
         <v>117</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="25" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="25" t="s">
+      <c r="A18" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="26" t="s">
+      <c r="B18" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="25" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
+      <c r="A19" s="2"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29" t="s">
+      <c r="A20" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="24" t="s">
+      <c r="A21" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="B21" s="24" t="s">
+      <c r="B21" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="C21" s="24" t="s">
+      <c r="C21" s="23" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="25" t="s">
+      <c r="A22" s="24" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="25" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="25" t="s">
+      <c r="A23" s="24" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="C23" s="26" t="s">
+      <c r="C23" s="25" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25" t="s">
+      <c r="A24" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C24" s="25" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25" t="s">
+      <c r="A25" s="24" t="s">
         <v>136</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C25" s="25" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="24" t="s">
         <v>139</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C26" s="25" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
+      <c r="A27" s="24" t="s">
         <v>142</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="C27" s="26" t="s">
+      <c r="C27" s="25" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="3"/>
-      <c r="B28" s="3"/>
-      <c r="C28" s="3"/>
+      <c r="A28" s="2"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="29" t="s">
+      <c r="A29" s="28" t="s">
         <v>145</v>
       </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="C30" s="31"/>
+      <c r="C30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="C31" s="31"/>
+      <c r="C31" s="30"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="C32" s="31"/>
+      <c r="C32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="C33" s="31"/>
+      <c r="C33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="C34" s="31"/>
+      <c r="C34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="C35" s="31"/>
+      <c r="C35" s="30"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
+      <c r="A36" s="2"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="31" t="s">
         <v>153</v>
       </c>
-      <c r="B37" s="32"/>
-      <c r="C37" s="32"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="2"/>
+      <c r="C38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="32" t="s">
+      <c r="A39" s="31" t="s">
         <v>154</v>
       </c>
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3"/>
-      <c r="C40" s="3"/>
+      <c r="A40" s="2"/>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="32" t="s">
+      <c r="A41" s="31" t="s">
         <v>155</v>
       </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
+      <c r="B41" s="31"/>
+      <c r="C41" s="31"/>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>

--- a/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
+++ b/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="160">
   <si>
     <t xml:space="preserve">Bryan Rogers - Chief Operating Officer</t>
   </si>
@@ -92,6 +92,18 @@
     <t xml:space="preserve">BizBuySell 2025: median seller's discretionary earnings for a bar was $128,375 on $800,000 of revenue - pre-tax and before debt service. REPLACE THIS WITH YOUR REAL NUMBER. The whole comparison turns on it.</t>
   </si>
   <si>
+    <t xml:space="preserve">Share of full-time you work today (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About three days a week while the bar is still yours. Salary and bonus below are scaled by this until the year you go full-time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year you go full-time (1-15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The year the bar is sold or handed off and you are at 100%. Change it if that timeline moves.</t>
+  </si>
+  <si>
     <t xml:space="preserve">What you earn, year by year</t>
   </si>
   <si>
@@ -107,10 +119,10 @@
     <t xml:space="preserve">Company revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Base salary (steps with the size of the company)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The raise happens when the business gets there - and you are the person most able to make it get there.</t>
+    <t xml:space="preserve">Base salary (steps with the size of the company, ramped while you still run the bar)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The raise happens when the business gets there - and you are the person most able to make it get there. Scaled down to your actual share of full-time until the year you go full-time, set above.</t>
   </si>
   <si>
     <t xml:space="preserve">Bonus earned</t>
@@ -1051,7 +1063,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1186,6 +1198,28 @@
       </c>
       <c r="C13" s="6" t="s">
         <v>21</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="7" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1215,7 +1249,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1237,7 +1271,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1299,7 +1333,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>1</v>
@@ -1348,12 +1382,12 @@
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1107883.476</v>
@@ -1403,82 +1437,82 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B7" s="12" t="n">
-        <f aca="false">IF(B6&gt;=6000000,'Your numbers'!$B$7,IF(B6&gt;=3000000,'Your numbers'!$B$6,IF(B6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(B6&gt;=6000000,'Your numbers'!$B$7,IF(B6&gt;=3000000,'Your numbers'!$B$6,IF(B6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(1&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <v>57000</v>
+      </c>
+      <c r="C7" s="12" t="n">
+        <f aca="false">IF(C6&gt;=6000000,'Your numbers'!$B$7,IF(C6&gt;=3000000,'Your numbers'!$B$6,IF(C6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(2&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>95000</v>
       </c>
-      <c r="C7" s="12" t="n">
-        <f aca="false">IF(C6&gt;=6000000,'Your numbers'!$B$7,IF(C6&gt;=3000000,'Your numbers'!$B$6,IF(C6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+      <c r="D7" s="12" t="n">
+        <f aca="false">IF(D6&gt;=6000000,'Your numbers'!$B$7,IF(D6&gt;=3000000,'Your numbers'!$B$6,IF(D6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(3&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>95000</v>
       </c>
-      <c r="D7" s="12" t="n">
-        <f aca="false">IF(D6&gt;=6000000,'Your numbers'!$B$7,IF(D6&gt;=3000000,'Your numbers'!$B$6,IF(D6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
-        <v>95000</v>
-      </c>
       <c r="E7" s="12" t="n">
-        <f aca="false">IF(E6&gt;=6000000,'Your numbers'!$B$7,IF(E6&gt;=3000000,'Your numbers'!$B$6,IF(E6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(E6&gt;=6000000,'Your numbers'!$B$7,IF(E6&gt;=3000000,'Your numbers'!$B$6,IF(E6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(4&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>120000</v>
       </c>
       <c r="F7" s="12" t="n">
-        <f aca="false">IF(F6&gt;=6000000,'Your numbers'!$B$7,IF(F6&gt;=3000000,'Your numbers'!$B$6,IF(F6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(F6&gt;=6000000,'Your numbers'!$B$7,IF(F6&gt;=3000000,'Your numbers'!$B$6,IF(F6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(5&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>120000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <f aca="false">IF(G6&gt;=6000000,'Your numbers'!$B$7,IF(G6&gt;=3000000,'Your numbers'!$B$6,IF(G6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(G6&gt;=6000000,'Your numbers'!$B$7,IF(G6&gt;=3000000,'Your numbers'!$B$6,IF(G6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(6&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>120000</v>
       </c>
       <c r="H7" s="12" t="n">
-        <f aca="false">IF(H6&gt;=6000000,'Your numbers'!$B$7,IF(H6&gt;=3000000,'Your numbers'!$B$6,IF(H6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(H6&gt;=6000000,'Your numbers'!$B$7,IF(H6&gt;=3000000,'Your numbers'!$B$6,IF(H6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(7&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>155000</v>
       </c>
       <c r="I7" s="12" t="n">
-        <f aca="false">IF(I6&gt;=6000000,'Your numbers'!$B$7,IF(I6&gt;=3000000,'Your numbers'!$B$6,IF(I6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(I6&gt;=6000000,'Your numbers'!$B$7,IF(I6&gt;=3000000,'Your numbers'!$B$6,IF(I6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(8&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>155000</v>
       </c>
       <c r="J7" s="12" t="n">
-        <f aca="false">IF(J6&gt;=6000000,'Your numbers'!$B$7,IF(J6&gt;=3000000,'Your numbers'!$B$6,IF(J6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(J6&gt;=6000000,'Your numbers'!$B$7,IF(J6&gt;=3000000,'Your numbers'!$B$6,IF(J6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(9&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>155000</v>
       </c>
       <c r="K7" s="12" t="n">
-        <f aca="false">IF(K6&gt;=6000000,'Your numbers'!$B$7,IF(K6&gt;=3000000,'Your numbers'!$B$6,IF(K6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(K6&gt;=6000000,'Your numbers'!$B$7,IF(K6&gt;=3000000,'Your numbers'!$B$6,IF(K6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(10&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>155000</v>
       </c>
       <c r="L7" s="12" t="n">
-        <f aca="false">IF(L6&gt;=6000000,'Your numbers'!$B$7,IF(L6&gt;=3000000,'Your numbers'!$B$6,IF(L6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(L6&gt;=6000000,'Your numbers'!$B$7,IF(L6&gt;=3000000,'Your numbers'!$B$6,IF(L6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(11&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>155000</v>
       </c>
       <c r="M7" s="12" t="n">
-        <f aca="false">IF(M6&gt;=6000000,'Your numbers'!$B$7,IF(M6&gt;=3000000,'Your numbers'!$B$6,IF(M6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(M6&gt;=6000000,'Your numbers'!$B$7,IF(M6&gt;=3000000,'Your numbers'!$B$6,IF(M6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(12&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>185000</v>
       </c>
       <c r="N7" s="12" t="n">
-        <f aca="false">IF(N6&gt;=6000000,'Your numbers'!$B$7,IF(N6&gt;=3000000,'Your numbers'!$B$6,IF(N6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(N6&gt;=6000000,'Your numbers'!$B$7,IF(N6&gt;=3000000,'Your numbers'!$B$6,IF(N6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(13&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>185000</v>
       </c>
       <c r="O7" s="12" t="n">
-        <f aca="false">IF(O6&gt;=6000000,'Your numbers'!$B$7,IF(O6&gt;=3000000,'Your numbers'!$B$6,IF(O6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(O6&gt;=6000000,'Your numbers'!$B$7,IF(O6&gt;=3000000,'Your numbers'!$B$6,IF(O6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(14&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>185000</v>
       </c>
       <c r="P7" s="12" t="n">
-        <f aca="false">IF(P6&gt;=6000000,'Your numbers'!$B$7,IF(P6&gt;=3000000,'Your numbers'!$B$6,IF(P6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))</f>
+        <f aca="false">IF(P6&gt;=6000000,'Your numbers'!$B$7,IF(P6&gt;=3000000,'Your numbers'!$B$6,IF(P6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(15&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
         <v>185000</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="6" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B8" s="12" t="n">
         <f aca="false">B7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
-        <v>20900</v>
+        <v>12540</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">C7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
@@ -1541,11 +1575,11 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">B7+B8</f>
-        <v>115900</v>
+        <v>69540</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">C7+C8</f>
@@ -1608,7 +1642,7 @@
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>0</v>
@@ -1657,16 +1691,16 @@
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">B9-B10</f>
-        <v>115900</v>
+        <v>69540</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">C9-C10</f>
@@ -1729,7 +1763,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -1751,7 +1785,7 @@
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,1/'Your numbers'!$B$11))</f>
@@ -1815,12 +1849,12 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">B13*'Your numbers'!$B$10</f>
@@ -1887,7 +1921,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>691314.397345807</v>
@@ -1939,7 +1973,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">MAX(0,B15-'Your numbers'!$B$12)</f>
@@ -2006,7 +2040,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">B14*B16</f>
@@ -2073,7 +2107,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -2095,7 +2129,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^0</f>
@@ -2159,16 +2193,16 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">B9-B19</f>
-        <v>-12475</v>
+        <v>-58835</v>
       </c>
       <c r="C20" s="11" t="n">
         <f aca="false">C9-C19</f>
@@ -2228,148 +2262,148 @@
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="6" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">B20</f>
-        <v>-12475</v>
+        <v>-58835</v>
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">B21+C20</f>
-        <v>-28480.3125</v>
+        <v>-74840.3125</v>
       </c>
       <c r="D21" s="11" t="n">
         <f aca="false">C21+D20</f>
-        <v>-48113.02109375</v>
+        <v>-94473.02109375</v>
       </c>
       <c r="E21" s="11" t="n">
         <f aca="false">D21+E20</f>
-        <v>-40972.8791738282</v>
+        <v>-87332.8791738282</v>
       </c>
       <c r="F21" s="11" t="n">
         <f aca="false">E21+F20</f>
-        <v>-37662.3833511085</v>
+        <v>-84022.3833511085</v>
       </c>
       <c r="G21" s="11" t="n">
         <f aca="false">F21+G20</f>
-        <v>-38286.848893264</v>
+        <v>-84646.848893264</v>
       </c>
       <c r="H21" s="11" t="n">
         <f aca="false">G21+H20</f>
-        <v>-254.487237828842</v>
+        <v>-46614.4872378288</v>
       </c>
       <c r="I21" s="11" t="n">
         <f aca="false">H21+I20</f>
-        <v>33623.5143631308</v>
+        <v>-12736.4856368692</v>
       </c>
       <c r="J21" s="11" t="n">
         <f aca="false">I21+J20</f>
-        <v>63232.9110081168</v>
+        <v>16872.9110081168</v>
       </c>
       <c r="K21" s="11" t="n">
         <f aca="false">J21+K20</f>
-        <v>88456.3160608399</v>
+        <v>42096.3160608399</v>
       </c>
       <c r="L21" s="11" t="n">
         <f aca="false">K21+L20</f>
-        <v>109173.114752513</v>
+        <v>62813.1147525129</v>
       </c>
       <c r="M21" s="11" t="n">
         <f aca="false">L21+M20</f>
-        <v>161859.375408207</v>
+        <v>115499.375408207</v>
       </c>
       <c r="N21" s="11" t="n">
         <f aca="false">M21+N20</f>
-        <v>209787.758231932</v>
+        <v>163427.758231932</v>
       </c>
       <c r="O21" s="11" t="n">
         <f aca="false">N21+O20</f>
-        <v>252827.42158331</v>
+        <v>206467.42158331</v>
       </c>
       <c r="P21" s="11" t="n">
         <f aca="false">O21+P20</f>
-        <v>290843.925676851</v>
+        <v>244483.925676851</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B22" s="11" t="n">
         <f aca="false">B21+B17</f>
-        <v>-12475</v>
+        <v>-58835</v>
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">C21+C17</f>
-        <v>-26688.1195063306</v>
+        <v>-73048.1195063306</v>
       </c>
       <c r="D22" s="11" t="n">
         <f aca="false">D21+D17</f>
-        <v>-29815.164263956</v>
+        <v>-76175.164263956</v>
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">E21+E17</f>
-        <v>81415.5149731138</v>
+        <v>35055.5149731138</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">F21+F17</f>
-        <v>94794.715754352</v>
+        <v>48434.715754352</v>
       </c>
       <c r="G22" s="11" t="n">
         <f aca="false">G21+G17</f>
-        <v>100587.251734994</v>
+        <v>54227.251734994</v>
       </c>
       <c r="H22" s="11" t="n">
         <f aca="false">H21+H17</f>
-        <v>221032.596821044</v>
+        <v>174672.596821044</v>
       </c>
       <c r="I22" s="11" t="n">
         <f aca="false">I21+I17</f>
-        <v>347573.428938037</v>
+        <v>301213.428938037</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">J21+J17</f>
-        <v>480453.361804062</v>
+        <v>434093.361804062</v>
       </c>
       <c r="K22" s="11" t="n">
         <f aca="false">K21+K17</f>
-        <v>547935.24594627</v>
+        <v>501575.24594627</v>
       </c>
       <c r="L22" s="11" t="n">
         <f aca="false">L21+L17</f>
-        <v>924192.699531582</v>
+        <v>877832.699531582</v>
       </c>
       <c r="M22" s="11" t="n">
         <f aca="false">M21+M17</f>
-        <v>1151084.54313073</v>
+        <v>1104724.54313073</v>
       </c>
       <c r="N22" s="11" t="n">
         <f aca="false">N21+N17</f>
-        <v>1387496.42211359</v>
+        <v>1341136.42211359</v>
       </c>
       <c r="O22" s="11" t="n">
         <f aca="false">O21+O17</f>
-        <v>1547677.51720044</v>
+        <v>1501317.51720044</v>
       </c>
       <c r="P22" s="11" t="n">
         <f aca="false">P21+P17</f>
-        <v>1702965.08255656</v>
+        <v>1656605.08255656</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="6" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="4" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B23" s="19" t="str">
         <f aca="false">IF(B22&gt;0,"AHEAD","behind")</f>
@@ -2461,7 +2495,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2483,7 +2517,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2525,7 +2559,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2567,7 +2601,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>1</v>
@@ -2616,12 +2650,12 @@
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1107883.476</v>
@@ -2673,7 +2707,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>2</v>
@@ -2725,7 +2759,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>9</v>
@@ -2777,7 +2811,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>314146.07309104</v>
@@ -2826,12 +2860,12 @@
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="6" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>62958.4292364159</v>
@@ -2883,7 +2917,7 @@
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>691314.397345807</v>
@@ -2932,7 +2966,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -2962,7 +2996,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2984,7 +3018,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3026,14 +3060,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>0.2</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="20" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3052,14 +3086,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>0.0875</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="20" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -3118,7 +3152,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>1</v>
@@ -3167,12 +3201,12 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="9" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">'Year by year'!B17</f>
@@ -3236,12 +3270,12 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="6" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">B9*(1-$B$4)</f>
@@ -3308,7 +3342,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">B10</f>
@@ -3375,7 +3409,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,36,-B10))</f>
@@ -3442,7 +3476,7 @@
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,60,-B10))</f>
@@ -3506,12 +3540,12 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,84,-B10))</f>
@@ -3578,7 +3612,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -3600,7 +3634,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>314146.07309104</v>
@@ -3652,7 +3686,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>62958.4292364159</v>
@@ -3704,7 +3738,7 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">IF(B16=0,0,B13*12/B16)</f>
@@ -3768,12 +3802,12 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B19" s="19" t="str">
         <f aca="false">IF(B10=0,"-",IF(B17&gt;=B10,"yes","no - needs a note"))</f>
@@ -3860,7 +3894,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -3882,7 +3916,7 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -3904,7 +3938,7 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -3926,7 +3960,7 @@
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -3948,7 +3982,7 @@
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -3970,7 +4004,7 @@
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -3992,7 +4026,7 @@
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -4047,14 +4081,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4066,75 +4100,75 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4144,75 +4178,75 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4222,86 +4256,86 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4311,62 +4345,62 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C31" s="30"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="C35" s="30"/>
     </row>
@@ -4377,7 +4411,7 @@
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -4389,7 +4423,7 @@
     </row>
     <row r="39" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
@@ -4401,7 +4435,7 @@
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>

--- a/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
+++ b/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
@@ -1924,49 +1924,49 @@
         <v>42</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>691314.397345807</v>
+        <v>737130.151233105</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>752384.283227823</v>
+        <v>793606.669249441</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>925823.920331045</v>
+        <v>973791.845154872</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>1742417.68455785</v>
+        <v>1704841.10205784</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>1826323.55921217</v>
+        <v>1781926.25021217</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>1879798.57190215</v>
+        <v>2078739.72158601</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>2566573.43382394</v>
+        <v>2788865.52166945</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>3338763.68812422</v>
+        <v>3584726.63004211</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>4199351.48996621</v>
+        <v>4191175.85367095</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>4551505.48237858</v>
+        <v>5168218.95382355</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>7514344.27315891</v>
+        <v>8245690.54355842</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>8966057.46435439</v>
+        <v>9739722.17619467</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>10536753.2656805</v>
+        <v>11353079.965143</v>
       </c>
       <c r="O15" s="12" t="n">
-        <v>11512931.8634761</v>
+        <v>12401842.2665323</v>
       </c>
       <c r="P15" s="12" t="n">
-        <v>12490190.7073309</v>
+        <v>13454921.9845546</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -1977,63 +1977,63 @@
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">MAX(0,B15-'Your numbers'!$B$12)</f>
-        <v>0</v>
+        <v>14615.751233105</v>
       </c>
       <c r="C16" s="12" t="n">
         <f aca="false">MAX(0,C15-'Your numbers'!$B$12)</f>
-        <v>29869.883227823</v>
+        <v>71092.269249441</v>
       </c>
       <c r="D16" s="12" t="n">
         <f aca="false">MAX(0,D15-'Your numbers'!$B$12)</f>
-        <v>203309.520331045</v>
+        <v>251277.445154872</v>
       </c>
       <c r="E16" s="12" t="n">
         <f aca="false">MAX(0,E15-'Your numbers'!$B$12)</f>
-        <v>1019903.28455785</v>
+        <v>982326.70205784</v>
       </c>
       <c r="F16" s="12" t="n">
         <f aca="false">MAX(0,F15-'Your numbers'!$B$12)</f>
-        <v>1103809.15921217</v>
+        <v>1059411.85021217</v>
       </c>
       <c r="G16" s="12" t="n">
         <f aca="false">MAX(0,G15-'Your numbers'!$B$12)</f>
-        <v>1157284.17190215</v>
+        <v>1356225.32158601</v>
       </c>
       <c r="H16" s="12" t="n">
         <f aca="false">MAX(0,H15-'Your numbers'!$B$12)</f>
-        <v>1844059.03382394</v>
+        <v>2066351.12166945</v>
       </c>
       <c r="I16" s="12" t="n">
         <f aca="false">MAX(0,I15-'Your numbers'!$B$12)</f>
-        <v>2616249.28812422</v>
+        <v>2862212.23004211</v>
       </c>
       <c r="J16" s="12" t="n">
         <f aca="false">MAX(0,J15-'Your numbers'!$B$12)</f>
-        <v>3476837.08996621</v>
+        <v>3468661.45367095</v>
       </c>
       <c r="K16" s="12" t="n">
         <f aca="false">MAX(0,K15-'Your numbers'!$B$12)</f>
-        <v>3828991.08237858</v>
+        <v>4445704.55382355</v>
       </c>
       <c r="L16" s="12" t="n">
         <f aca="false">MAX(0,L15-'Your numbers'!$B$12)</f>
-        <v>6791829.87315891</v>
+        <v>7523176.14355842</v>
       </c>
       <c r="M16" s="12" t="n">
         <f aca="false">MAX(0,M15-'Your numbers'!$B$12)</f>
-        <v>8243543.06435439</v>
+        <v>9017207.77619467</v>
       </c>
       <c r="N16" s="12" t="n">
         <f aca="false">MAX(0,N15-'Your numbers'!$B$12)</f>
-        <v>9814238.8656805</v>
+        <v>10630565.565143</v>
       </c>
       <c r="O16" s="12" t="n">
         <f aca="false">MAX(0,O15-'Your numbers'!$B$12)</f>
-        <v>10790417.4634761</v>
+        <v>11679327.8665323</v>
       </c>
       <c r="P16" s="12" t="n">
         <f aca="false">MAX(0,P15-'Your numbers'!$B$12)</f>
-        <v>11767676.3073309</v>
+        <v>12732407.5845546</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -2044,63 +2044,63 @@
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">B14*B16</f>
-        <v>0</v>
+        <v>438.472536993149</v>
       </c>
       <c r="C17" s="11" t="n">
         <f aca="false">C14*C16</f>
-        <v>1792.19299366938</v>
+        <v>4265.53615496646</v>
       </c>
       <c r="D17" s="11" t="n">
         <f aca="false">D14*D16</f>
-        <v>18297.8568297941</v>
+        <v>22614.9700639385</v>
       </c>
       <c r="E17" s="11" t="n">
         <f aca="false">E14*E16</f>
-        <v>122388.394146942</v>
+        <v>117879.204246941</v>
       </c>
       <c r="F17" s="11" t="n">
         <f aca="false">F14*F16</f>
-        <v>132457.09910546</v>
+        <v>127129.42202546</v>
       </c>
       <c r="G17" s="11" t="n">
         <f aca="false">G14*G16</f>
-        <v>138874.100628258</v>
+        <v>162747.038590321</v>
       </c>
       <c r="H17" s="11" t="n">
         <f aca="false">H14*H16</f>
-        <v>221287.084058873</v>
+        <v>247962.134600334</v>
       </c>
       <c r="I17" s="11" t="n">
         <f aca="false">I14*I16</f>
-        <v>313949.914574906</v>
+        <v>343465.467605053</v>
       </c>
       <c r="J17" s="11" t="n">
         <f aca="false">J14*J16</f>
-        <v>417220.450795945</v>
+        <v>416239.374440514</v>
       </c>
       <c r="K17" s="11" t="n">
         <f aca="false">K14*K16</f>
-        <v>459478.92988543</v>
+        <v>533484.546458826</v>
       </c>
       <c r="L17" s="11" t="n">
         <f aca="false">L14*L16</f>
-        <v>815019.584779069</v>
+        <v>902781.13722701</v>
       </c>
       <c r="M17" s="11" t="n">
         <f aca="false">M14*M16</f>
-        <v>989225.167722527</v>
+        <v>1082064.93314336</v>
       </c>
       <c r="N17" s="11" t="n">
         <f aca="false">N14*N16</f>
-        <v>1177708.66388166</v>
+        <v>1275667.86781716</v>
       </c>
       <c r="O17" s="11" t="n">
         <f aca="false">O14*O16</f>
-        <v>1294850.09561713</v>
+        <v>1401519.34398388</v>
       </c>
       <c r="P17" s="11" t="n">
         <f aca="false">P14*P16</f>
-        <v>1412121.15687971</v>
+        <v>1527888.91014655</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -2338,63 +2338,63 @@
       </c>
       <c r="B22" s="11" t="n">
         <f aca="false">B21+B17</f>
-        <v>-58835</v>
+        <v>-58396.5274630069</v>
       </c>
       <c r="C22" s="11" t="n">
         <f aca="false">C21+C17</f>
-        <v>-73048.1195063306</v>
+        <v>-70574.7763450336</v>
       </c>
       <c r="D22" s="11" t="n">
         <f aca="false">D21+D17</f>
-        <v>-76175.164263956</v>
+        <v>-71858.0510298115</v>
       </c>
       <c r="E22" s="11" t="n">
         <f aca="false">E21+E17</f>
-        <v>35055.5149731138</v>
+        <v>30546.3250731126</v>
       </c>
       <c r="F22" s="11" t="n">
         <f aca="false">F21+F17</f>
-        <v>48434.715754352</v>
+        <v>43107.0386743519</v>
       </c>
       <c r="G22" s="11" t="n">
         <f aca="false">G21+G17</f>
-        <v>54227.251734994</v>
+        <v>78100.1896970572</v>
       </c>
       <c r="H22" s="11" t="n">
         <f aca="false">H21+H17</f>
-        <v>174672.596821044</v>
+        <v>201347.647362505</v>
       </c>
       <c r="I22" s="11" t="n">
         <f aca="false">I21+I17</f>
-        <v>301213.428938037</v>
+        <v>330728.981968184</v>
       </c>
       <c r="J22" s="11" t="n">
         <f aca="false">J21+J17</f>
-        <v>434093.361804062</v>
+        <v>433112.285448631</v>
       </c>
       <c r="K22" s="11" t="n">
         <f aca="false">K21+K17</f>
-        <v>501575.24594627</v>
+        <v>575580.862519666</v>
       </c>
       <c r="L22" s="11" t="n">
         <f aca="false">L21+L17</f>
-        <v>877832.699531582</v>
+        <v>965594.251979523</v>
       </c>
       <c r="M22" s="11" t="n">
         <f aca="false">M21+M17</f>
-        <v>1104724.54313073</v>
+        <v>1197564.30855157</v>
       </c>
       <c r="N22" s="11" t="n">
         <f aca="false">N21+N17</f>
-        <v>1341136.42211359</v>
+        <v>1439095.62604909</v>
       </c>
       <c r="O22" s="11" t="n">
         <f aca="false">O21+O17</f>
-        <v>1501317.51720044</v>
+        <v>1607986.76556719</v>
       </c>
       <c r="P22" s="11" t="n">
         <f aca="false">P21+P17</f>
-        <v>1656605.08255656</v>
+        <v>1772372.8358234</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="6" t="s">
@@ -2777,34 +2777,34 @@
         <v>19</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H9" s="19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I9" s="19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J9" s="19" t="n">
         <v>28</v>
       </c>
       <c r="K9" s="19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L9" s="19" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="M9" s="19" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="N9" s="19" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O9" s="19" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="P9" s="19" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
@@ -2814,49 +2814,49 @@
         <v>60</v>
       </c>
       <c r="B10" s="11" t="n">
-        <v>314146.07309104</v>
+        <v>309346.07309104</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>303726.24221904</v>
+        <v>298686.24221904</v>
       </c>
       <c r="D10" s="11" t="n">
-        <v>361218.979335931</v>
+        <v>355430.854335931</v>
       </c>
       <c r="E10" s="11" t="n">
-        <v>487332.012318055</v>
+        <v>480212.618568055</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>479969.659557169</v>
+        <v>471947.318307169</v>
       </c>
       <c r="G10" s="11" t="n">
-        <v>466088.769207364</v>
+        <v>514099.926862789</v>
       </c>
       <c r="H10" s="11" t="n">
-        <v>597197.758851492</v>
+        <v>646151.297211341</v>
       </c>
       <c r="I10" s="11" t="n">
-        <v>735647.486330165</v>
+        <v>785530.442582843</v>
       </c>
       <c r="J10" s="11" t="n">
-        <v>881486.5874483</v>
+        <v>869075.961720472</v>
       </c>
       <c r="K10" s="11" t="n">
-        <v>898428.470548401</v>
+        <v>1029166.33528225</v>
       </c>
       <c r="L10" s="11" t="n">
-        <v>1062695.91705148</v>
+        <v>1197070.66564829</v>
       </c>
       <c r="M10" s="11" t="n">
-        <v>1234746.42040954</v>
+        <v>1372827.40169565</v>
       </c>
       <c r="N10" s="11" t="n">
-        <v>1414609.86275326</v>
+        <v>1556465.40590655</v>
       </c>
       <c r="O10" s="11" t="n">
-        <v>1480797.94885832</v>
+        <v>1627343.6700041</v>
       </c>
       <c r="P10" s="11" t="n">
-        <v>1544843.49387317</v>
+        <v>1696229.81094027</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="6" t="s">
@@ -2868,49 +2868,49 @@
         <v>62</v>
       </c>
       <c r="B11" s="12" t="n">
-        <v>62958.4292364159</v>
+        <v>61038.4292364159</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>124448.926124032</v>
+        <v>120512.926124032</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>195086.517858404</v>
+        <v>188835.267858404</v>
       </c>
       <c r="E11" s="12" t="n">
-        <v>302319.322785626</v>
+        <v>293220.315285626</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>420457.186608494</v>
+        <v>408149.242608494</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>533042.694291439</v>
+        <v>539939.213353609</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>698071.797832036</v>
+        <v>724549.732238146</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>918480.792364102</v>
+        <v>964911.909271283</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1197225.42734342</v>
+        <v>1238692.29395947</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>1482746.81556278</v>
+        <v>1576508.82807237</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>1833975.18238338</v>
+        <v>1981487.09433169</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>2254023.75054719</v>
+        <v>2456768.05500994</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>2746017.69564849</v>
+        <v>3005504.21737256</v>
       </c>
       <c r="O11" s="12" t="n">
-        <v>3278336.87519182</v>
+        <v>3596441.6853742</v>
       </c>
       <c r="P11" s="12" t="n">
-        <v>3836274.27274109</v>
+        <v>4214933.60975031</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -2920,49 +2920,49 @@
         <v>42</v>
       </c>
       <c r="B12" s="11" t="n">
-        <v>691314.397345807</v>
+        <v>737130.151233105</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>752384.283227823</v>
+        <v>793606.669249441</v>
       </c>
       <c r="D12" s="11" t="n">
-        <v>925823.920331045</v>
+        <v>973791.845154872</v>
       </c>
       <c r="E12" s="11" t="n">
-        <v>1742417.68455785</v>
+        <v>1704841.10205784</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>1826323.55921217</v>
+        <v>1781926.25021217</v>
       </c>
       <c r="G12" s="11" t="n">
-        <v>1879798.57190215</v>
+        <v>2078739.72158601</v>
       </c>
       <c r="H12" s="11" t="n">
-        <v>2566573.43382394</v>
+        <v>2788865.52166945</v>
       </c>
       <c r="I12" s="11" t="n">
-        <v>3338763.68812422</v>
+        <v>3584726.63004211</v>
       </c>
       <c r="J12" s="11" t="n">
-        <v>4199351.48996621</v>
+        <v>4191175.85367095</v>
       </c>
       <c r="K12" s="11" t="n">
-        <v>4551505.48237858</v>
+        <v>5168218.95382355</v>
       </c>
       <c r="L12" s="11" t="n">
-        <v>7514344.27315891</v>
+        <v>8245690.54355842</v>
       </c>
       <c r="M12" s="11" t="n">
-        <v>8966057.46435439</v>
+        <v>9739722.17619467</v>
       </c>
       <c r="N12" s="11" t="n">
-        <v>10536753.2656805</v>
+        <v>11353079.965143</v>
       </c>
       <c r="O12" s="11" t="n">
-        <v>11512931.8634761</v>
+        <v>12401842.2665323</v>
       </c>
       <c r="P12" s="11" t="n">
-        <v>12490190.7073309</v>
+        <v>13454921.9845546</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
@@ -3210,63 +3210,63 @@
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">'Year by year'!B17</f>
-        <v>0</v>
+        <v>438.472536993149</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">'Year by year'!C17</f>
-        <v>1792.19299366938</v>
+        <v>4265.53615496646</v>
       </c>
       <c r="D9" s="11" t="n">
         <f aca="false">'Year by year'!D17</f>
-        <v>18297.8568297941</v>
+        <v>22614.9700639385</v>
       </c>
       <c r="E9" s="11" t="n">
         <f aca="false">'Year by year'!E17</f>
-        <v>122388.394146942</v>
+        <v>117879.204246941</v>
       </c>
       <c r="F9" s="11" t="n">
         <f aca="false">'Year by year'!F17</f>
-        <v>132457.09910546</v>
+        <v>127129.42202546</v>
       </c>
       <c r="G9" s="11" t="n">
         <f aca="false">'Year by year'!G17</f>
-        <v>138874.100628258</v>
+        <v>162747.038590321</v>
       </c>
       <c r="H9" s="11" t="n">
         <f aca="false">'Year by year'!H17</f>
-        <v>221287.084058873</v>
+        <v>247962.134600334</v>
       </c>
       <c r="I9" s="11" t="n">
         <f aca="false">'Year by year'!I17</f>
-        <v>313949.914574906</v>
+        <v>343465.467605053</v>
       </c>
       <c r="J9" s="11" t="n">
         <f aca="false">'Year by year'!J17</f>
-        <v>417220.450795945</v>
+        <v>416239.374440514</v>
       </c>
       <c r="K9" s="11" t="n">
         <f aca="false">'Year by year'!K17</f>
-        <v>459478.92988543</v>
+        <v>533484.546458826</v>
       </c>
       <c r="L9" s="11" t="n">
         <f aca="false">'Year by year'!L17</f>
-        <v>815019.584779069</v>
+        <v>902781.13722701</v>
       </c>
       <c r="M9" s="11" t="n">
         <f aca="false">'Year by year'!M17</f>
-        <v>989225.167722527</v>
+        <v>1082064.93314336</v>
       </c>
       <c r="N9" s="11" t="n">
         <f aca="false">'Year by year'!N17</f>
-        <v>1177708.66388166</v>
+        <v>1275667.86781716</v>
       </c>
       <c r="O9" s="11" t="n">
         <f aca="false">'Year by year'!O17</f>
-        <v>1294850.09561713</v>
+        <v>1401519.34398388</v>
       </c>
       <c r="P9" s="11" t="n">
         <f aca="false">'Year by year'!P17</f>
-        <v>1412121.15687971</v>
+        <v>1527888.91014655</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="6" t="s">
@@ -3279,63 +3279,63 @@
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">B9*(1-$B$4)</f>
-        <v>0</v>
+        <v>350.778029594519</v>
       </c>
       <c r="C10" s="11" t="n">
         <f aca="false">C9*(1-$B$4)</f>
-        <v>1433.7543949355</v>
+        <v>3412.42892397317</v>
       </c>
       <c r="D10" s="11" t="n">
         <f aca="false">D9*(1-$B$4)</f>
-        <v>14638.2854638352</v>
+        <v>18091.9760511508</v>
       </c>
       <c r="E10" s="11" t="n">
         <f aca="false">E9*(1-$B$4)</f>
-        <v>97910.7153175536</v>
+        <v>94303.3633975526</v>
       </c>
       <c r="F10" s="11" t="n">
         <f aca="false">F9*(1-$B$4)</f>
-        <v>105965.679284368</v>
+        <v>101703.537620368</v>
       </c>
       <c r="G10" s="11" t="n">
         <f aca="false">G9*(1-$B$4)</f>
-        <v>111099.280502606</v>
+        <v>130197.630872257</v>
       </c>
       <c r="H10" s="11" t="n">
         <f aca="false">H9*(1-$B$4)</f>
-        <v>177029.667247098</v>
+        <v>198369.707680267</v>
       </c>
       <c r="I10" s="11" t="n">
         <f aca="false">I9*(1-$B$4)</f>
-        <v>251159.931659925</v>
+        <v>274772.374084043</v>
       </c>
       <c r="J10" s="11" t="n">
         <f aca="false">J9*(1-$B$4)</f>
-        <v>333776.360636756</v>
+        <v>332991.499552411</v>
       </c>
       <c r="K10" s="11" t="n">
         <f aca="false">K9*(1-$B$4)</f>
-        <v>367583.143908344</v>
+        <v>426787.637167061</v>
       </c>
       <c r="L10" s="11" t="n">
         <f aca="false">L9*(1-$B$4)</f>
-        <v>652015.667823255</v>
+        <v>722224.909781608</v>
       </c>
       <c r="M10" s="11" t="n">
         <f aca="false">M9*(1-$B$4)</f>
-        <v>791380.134178022</v>
+        <v>865651.946514688</v>
       </c>
       <c r="N10" s="11" t="n">
         <f aca="false">N9*(1-$B$4)</f>
-        <v>942166.931105328</v>
+        <v>1020534.29425373</v>
       </c>
       <c r="O10" s="11" t="n">
         <f aca="false">O9*(1-$B$4)</f>
-        <v>1035880.07649371</v>
+        <v>1121215.4751871</v>
       </c>
       <c r="P10" s="11" t="n">
         <f aca="false">P9*(1-$B$4)</f>
-        <v>1129696.92550377</v>
+        <v>1222311.12811724</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2"/>
@@ -3346,63 +3346,63 @@
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">B10</f>
-        <v>0</v>
+        <v>350.778029594519</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">C10</f>
-        <v>1433.7543949355</v>
+        <v>3412.42892397317</v>
       </c>
       <c r="D11" s="12" t="n">
         <f aca="false">D10</f>
-        <v>14638.2854638352</v>
+        <v>18091.9760511508</v>
       </c>
       <c r="E11" s="12" t="n">
         <f aca="false">E10</f>
-        <v>97910.7153175536</v>
+        <v>94303.3633975526</v>
       </c>
       <c r="F11" s="12" t="n">
         <f aca="false">F10</f>
-        <v>105965.679284368</v>
+        <v>101703.537620368</v>
       </c>
       <c r="G11" s="12" t="n">
         <f aca="false">G10</f>
-        <v>111099.280502606</v>
+        <v>130197.630872257</v>
       </c>
       <c r="H11" s="12" t="n">
         <f aca="false">H10</f>
-        <v>177029.667247098</v>
+        <v>198369.707680267</v>
       </c>
       <c r="I11" s="12" t="n">
         <f aca="false">I10</f>
-        <v>251159.931659925</v>
+        <v>274772.374084043</v>
       </c>
       <c r="J11" s="12" t="n">
         <f aca="false">J10</f>
-        <v>333776.360636756</v>
+        <v>332991.499552411</v>
       </c>
       <c r="K11" s="12" t="n">
         <f aca="false">K10</f>
-        <v>367583.143908344</v>
+        <v>426787.637167061</v>
       </c>
       <c r="L11" s="12" t="n">
         <f aca="false">L10</f>
-        <v>652015.667823255</v>
+        <v>722224.909781608</v>
       </c>
       <c r="M11" s="12" t="n">
         <f aca="false">M10</f>
-        <v>791380.134178022</v>
+        <v>865651.946514688</v>
       </c>
       <c r="N11" s="12" t="n">
         <f aca="false">N10</f>
-        <v>942166.931105328</v>
+        <v>1020534.29425373</v>
       </c>
       <c r="O11" s="12" t="n">
         <f aca="false">O10</f>
-        <v>1035880.07649371</v>
+        <v>1121215.4751871</v>
       </c>
       <c r="P11" s="12" t="n">
         <f aca="false">P10</f>
-        <v>1129696.92550377</v>
+        <v>1222311.12811724</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2"/>
@@ -3413,63 +3413,63 @@
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,36,-B10))</f>
-        <v>0</v>
+        <v>11.113878233567</v>
       </c>
       <c r="C12" s="12" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,36,-C10))</f>
-        <v>45.4263677248379</v>
+        <v>108.117716453278</v>
       </c>
       <c r="D12" s="12" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,36,-D10))</f>
-        <v>463.792223194017</v>
+        <v>573.217253855747</v>
       </c>
       <c r="E12" s="12" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,36,-E10))</f>
-        <v>3102.15485576049</v>
+        <v>2987.86129515506</v>
       </c>
       <c r="F12" s="12" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,36,-F10))</f>
-        <v>3357.3643647666</v>
+        <v>3222.32476857905</v>
       </c>
       <c r="G12" s="12" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,36,-G10))</f>
-        <v>3520.01485603352</v>
+        <v>4125.11757787631</v>
       </c>
       <c r="H12" s="12" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,36,-H10))</f>
-        <v>5608.92074052484</v>
+        <v>6285.04806568199</v>
       </c>
       <c r="I12" s="12" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,36,-I10))</f>
-        <v>7957.62750833079</v>
+        <v>8705.75249837679</v>
       </c>
       <c r="J12" s="12" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,36,-J10))</f>
-        <v>10575.2057323775</v>
+        <v>10550.3385805443</v>
       </c>
       <c r="K12" s="12" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,36,-K10))</f>
-        <v>11646.323194276</v>
+        <v>13522.1291839442</v>
       </c>
       <c r="L12" s="12" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,36,-L10))</f>
-        <v>20658.1431195734</v>
+        <v>22882.61814413</v>
       </c>
       <c r="M12" s="12" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,36,-M10))</f>
-        <v>25073.698195652</v>
+        <v>27426.889698125</v>
       </c>
       <c r="N12" s="12" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,36,-N10))</f>
-        <v>29851.1527649043</v>
+        <v>32334.1056810942</v>
       </c>
       <c r="O12" s="12" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,36,-O10))</f>
-        <v>32820.3138835038</v>
+        <v>35524.0386041986</v>
       </c>
       <c r="P12" s="12" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,36,-P10))</f>
-        <v>35792.7606965498</v>
+        <v>38727.1034538054</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2"/>
@@ -3480,63 +3480,63 @@
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,60,-B10))</f>
-        <v>0</v>
+        <v>7.23908782522604</v>
       </c>
       <c r="C13" s="11" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,60,-C10))</f>
-        <v>29.5887230928903</v>
+        <v>70.4230897999472</v>
       </c>
       <c r="D13" s="11" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,60,-D10))</f>
-        <v>302.093703547871</v>
+        <v>373.368319896091</v>
       </c>
       <c r="E13" s="11" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,60,-E10))</f>
-        <v>2020.60621651188</v>
+        <v>1946.16045548298</v>
       </c>
       <c r="F13" s="11" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,60,-F10))</f>
-        <v>2186.8383823411</v>
+        <v>2098.87957299117</v>
       </c>
       <c r="G13" s="11" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,60,-G10))</f>
-        <v>2292.78170530654</v>
+        <v>2686.91880620381</v>
       </c>
       <c r="H13" s="11" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,60,-H10))</f>
-        <v>3653.40243901156</v>
+        <v>4093.8018194065</v>
       </c>
       <c r="I13" s="11" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,60,-I10))</f>
-        <v>5183.2459563265</v>
+        <v>5670.54142541237</v>
       </c>
       <c r="J13" s="11" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,60,-J10))</f>
-        <v>6888.22042653823</v>
+        <v>6872.02306569798</v>
       </c>
       <c r="K13" s="11" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,60,-K10))</f>
-        <v>7585.89887998727</v>
+        <v>8807.71578466422</v>
       </c>
       <c r="L13" s="11" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,60,-L10))</f>
-        <v>13455.7990654432</v>
+        <v>14904.723529916</v>
       </c>
       <c r="M13" s="11" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,60,-M10))</f>
-        <v>16331.8959886859</v>
+        <v>17864.6606634443</v>
       </c>
       <c r="N13" s="11" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,60,-N10))</f>
-        <v>19443.7182060097</v>
+        <v>21061.003715933</v>
       </c>
       <c r="O13" s="11" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,60,-O10))</f>
-        <v>21377.6981950895</v>
+        <v>23138.7846760651</v>
       </c>
       <c r="P13" s="11" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,60,-P10))</f>
-        <v>23313.8183399425</v>
+        <v>25225.1191912451</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
@@ -3549,63 +3549,63 @@
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,84,-B10))</f>
-        <v>0</v>
+        <v>5.59929160095714</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">IF(C10=0,0,PMT($B$5/12,84,-C10))</f>
-        <v>22.886293507828</v>
+        <v>54.470870467438</v>
       </c>
       <c r="D14" s="12" t="n">
         <f aca="false">IF(D10=0,0,PMT($B$5/12,84,-D10))</f>
-        <v>233.663519191358</v>
+        <v>288.793028642719</v>
       </c>
       <c r="E14" s="12" t="n">
         <f aca="false">IF(E10=0,0,PMT($B$5/12,84,-E10))</f>
-        <v>1562.89904061269</v>
+        <v>1505.31671331954</v>
       </c>
       <c r="F14" s="12" t="n">
         <f aca="false">IF(F10=0,0,PMT($B$5/12,84,-F10))</f>
-        <v>1691.47634101413</v>
+        <v>1623.44193746579</v>
       </c>
       <c r="G14" s="12" t="n">
         <f aca="false">IF(G10=0,0,PMT($B$5/12,84,-G10))</f>
-        <v>1773.42141099804</v>
+        <v>2078.27868196377</v>
       </c>
       <c r="H14" s="12" t="n">
         <f aca="false">IF(H10=0,0,PMT($B$5/12,84,-H10))</f>
-        <v>2825.83470259736</v>
+        <v>3166.47493397003</v>
       </c>
       <c r="I14" s="12" t="n">
         <f aca="false">IF(I10=0,0,PMT($B$5/12,84,-I10))</f>
-        <v>4009.13847844467</v>
+        <v>4386.05190912981</v>
       </c>
       <c r="J14" s="12" t="n">
         <f aca="false">IF(J10=0,0,PMT($B$5/12,84,-J10))</f>
-        <v>5327.90259091139</v>
+        <v>5315.37425188579</v>
       </c>
       <c r="K14" s="12" t="n">
         <f aca="false">IF(K10=0,0,PMT($B$5/12,84,-K10))</f>
-        <v>5867.54310900995</v>
+        <v>6812.59437754481</v>
       </c>
       <c r="L14" s="12" t="n">
         <f aca="false">IF(L10=0,0,PMT($B$5/12,84,-L10))</f>
-        <v>10407.795085557</v>
+        <v>11528.5095706159</v>
       </c>
       <c r="M14" s="12" t="n">
         <f aca="false">IF(M10=0,0,PMT($B$5/12,84,-M10))</f>
-        <v>12632.3993084445</v>
+        <v>13817.962541938</v>
       </c>
       <c r="N14" s="12" t="n">
         <f aca="false">IF(N10=0,0,PMT($B$5/12,84,-N10))</f>
-        <v>15039.3323952922</v>
+        <v>16290.2708271354</v>
       </c>
       <c r="O14" s="12" t="n">
         <f aca="false">IF(O10=0,0,PMT($B$5/12,84,-O10))</f>
-        <v>16535.2277581773</v>
+        <v>17897.3934038439</v>
       </c>
       <c r="P14" s="12" t="n">
         <f aca="false">IF(P10=0,0,PMT($B$5/12,84,-P10))</f>
-        <v>18032.7784893264</v>
+        <v>19511.1319866148</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -3637,49 +3637,49 @@
         <v>79</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>314146.07309104</v>
+        <v>309346.07309104</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>303726.24221904</v>
+        <v>298686.24221904</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>361218.979335931</v>
+        <v>355430.854335931</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>487332.012318055</v>
+        <v>480212.618568055</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>479969.659557169</v>
+        <v>471947.318307169</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>466088.769207364</v>
+        <v>514099.926862789</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>597197.758851492</v>
+        <v>646151.297211341</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>735647.486330165</v>
+        <v>785530.442582843</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>881486.5874483</v>
+        <v>869075.961720472</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>898428.470548401</v>
+        <v>1029166.33528225</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>1062695.91705148</v>
+        <v>1197070.66564829</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>1234746.42040954</v>
+        <v>1372827.40169565</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>1414609.86275326</v>
+        <v>1556465.40590655</v>
       </c>
       <c r="O16" s="12" t="n">
-        <v>1480797.94885832</v>
+        <v>1627343.6700041</v>
       </c>
       <c r="P16" s="12" t="n">
-        <v>1544843.49387317</v>
+        <v>1696229.81094027</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -3689,49 +3689,49 @@
         <v>62</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>62958.4292364159</v>
+        <v>61038.4292364159</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>124448.926124032</v>
+        <v>120512.926124032</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>195086.517858404</v>
+        <v>188835.267858404</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>302319.322785626</v>
+        <v>293220.315285626</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>420457.186608494</v>
+        <v>408149.242608494</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>533042.694291439</v>
+        <v>539939.213353609</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>698071.797832036</v>
+        <v>724549.732238146</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>918480.792364102</v>
+        <v>964911.909271283</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>1197225.42734342</v>
+        <v>1238692.29395947</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>1482746.81556278</v>
+        <v>1576508.82807237</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>1833975.18238338</v>
+        <v>1981487.09433169</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>2254023.75054719</v>
+        <v>2456768.05500994</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>2746017.69564849</v>
+        <v>3005504.21737256</v>
       </c>
       <c r="O17" s="12" t="n">
-        <v>3278336.87519182</v>
+        <v>3596441.6853742</v>
       </c>
       <c r="P17" s="12" t="n">
-        <v>3836274.27274109</v>
+        <v>4214933.60975031</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2"/>
@@ -3742,63 +3742,63 @@
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">IF(B16=0,0,B13*12/B16)</f>
-        <v>0</v>
+        <v>0.000280815117627652</v>
       </c>
       <c r="C18" s="16" t="n">
         <f aca="false">IF(C16=0,0,C13*12/C16)</f>
-        <v>0.00116902864408608</v>
+        <v>0.00282931370163221</v>
       </c>
       <c r="D18" s="16" t="n">
         <f aca="false">IF(D16=0,0,D13*12/D16)</f>
-        <v>0.010035808332217</v>
+        <v>0.0126056018606603</v>
       </c>
       <c r="E18" s="16" t="n">
         <f aca="false">IF(E16=0,0,E13*12/E16)</f>
-        <v>0.0497551443066657</v>
+        <v>0.0486324693745757</v>
       </c>
       <c r="F18" s="16" t="n">
         <f aca="false">IF(F16=0,0,F13*12/F16)</f>
-        <v>0.0546744154876472</v>
+        <v>0.0533673016010258</v>
       </c>
       <c r="G18" s="16" t="n">
         <f aca="false">IF(G16=0,0,G13*12/G16)</f>
-        <v>0.0590303441777156</v>
+        <v>0.0627174290243601</v>
       </c>
       <c r="H18" s="16" t="n">
         <f aca="false">IF(H16=0,0,H13*12/H16)</f>
-        <v>0.0734109072218418</v>
+        <v>0.0760280479895256</v>
       </c>
       <c r="I18" s="16" t="n">
         <f aca="false">IF(I16=0,0,I13*12/I16)</f>
-        <v>0.0845499408775286</v>
+        <v>0.0866249013611872</v>
       </c>
       <c r="J18" s="16" t="n">
         <f aca="false">IF(J16=0,0,J13*12/J16)</f>
-        <v>0.0937718693573506</v>
+        <v>0.0948873060821114</v>
       </c>
       <c r="K18" s="16" t="n">
         <f aca="false">IF(K16=0,0,K13*12/K16)</f>
-        <v>0.101322241607372</v>
+        <v>0.102697285941621</v>
       </c>
       <c r="L18" s="16" t="n">
         <f aca="false">IF(L16=0,0,L13*12/L16)</f>
-        <v>0.151943360461313</v>
+        <v>0.149411966637851</v>
       </c>
       <c r="M18" s="16" t="n">
         <f aca="false">IF(M16=0,0,M13*12/M16)</f>
-        <v>0.158723077568613</v>
+        <v>0.156156504231009</v>
       </c>
       <c r="N18" s="16" t="n">
         <f aca="false">IF(N16=0,0,N13*12/N16)</f>
-        <v>0.164939199574076</v>
+        <v>0.162375625974157</v>
       </c>
       <c r="O18" s="16" t="n">
         <f aca="false">IF(O16=0,0,O13*12/O16)</f>
-        <v>0.17323928530483</v>
+        <v>0.170624940036226</v>
       </c>
       <c r="P18" s="16" t="n">
         <f aca="false">IF(P16=0,0,P13*12/P16)</f>
-        <v>0.181096545500472</v>
+        <v>0.178455435898243</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="6" t="s">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="B19" s="19" t="str">
         <f aca="false">IF(B10=0,"-",IF(B17&gt;=B10,"yes","no - needs a note"))</f>
-        <v>-</v>
+        <v>yes</v>
       </c>
       <c r="C19" s="19" t="str">
         <f aca="false">IF(C10=0,"-",IF(C17&gt;=C10,"yes","no - needs a note"))</f>

--- a/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
+++ b/docs/people/Scag-Scapes-Bryan-Proforma.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="165">
   <si>
     <t xml:space="preserve">Bryan Rogers - Chief Operating Officer</t>
   </si>
@@ -92,16 +92,22 @@
     <t xml:space="preserve">BizBuySell 2025: median seller's discretionary earnings for a bar was $128,375 on $800,000 of revenue - pre-tax and before debt service. REPLACE THIS WITH YOUR REAL NUMBER. The whole comparison turns on it.</t>
   </si>
   <si>
-    <t xml:space="preserve">Share of full-time you work today (%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">About three days a week while the bar is still yours. Salary and bonus below are scaled by this until the year you go full-time.</t>
+    <t xml:space="preserve">Hours you work a week today</t>
+  </si>
+  <si>
+    <t xml:space="preserve">About three days a week while the bar is still yours. Corrected Sept 2026 - this file used to model year 1 as a fraction of a COO salary you are not being paid. This is the real basis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Your hourly rate today ($/hr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What Charlie pays you right now. Until the year you go full-time, your pay below is hours x rate x 52 - your actual money, not a fraction of a salary band.</t>
   </si>
   <si>
     <t xml:space="preserve">Year you go full-time (1-15)</t>
   </si>
   <si>
-    <t xml:space="preserve">The year the bar is sold or handed off and you are at 100%. Change it if that timeline moves.</t>
+    <t xml:space="preserve">The year the bar is sold or handed off and you move onto the salary bands above. Before it you are hourly and there is no bonus; from it you are salaried and the bonus starts.</t>
   </si>
   <si>
     <t xml:space="preserve">What you earn, year by year</t>
@@ -119,13 +125,13 @@
     <t xml:space="preserve">Company revenue</t>
   </si>
   <si>
-    <t xml:space="preserve">Base salary (steps with the size of the company, ramped while you still run the bar)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The raise happens when the business gets there - and you are the person most able to make it get there. Scaled down to your actual share of full-time until the year you go full-time, set above.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bonus earned</t>
+    <t xml:space="preserve">Base pay - hourly today, salary once you are full-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before the year you go full-time this is your ACTUAL pay: hours a week x your hourly rate x 52. From that year it becomes the salary bands above, and the raise happens when the business gets there - which you are the person most able to make happen.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonus earned (starts when you go full-time)</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL CASH TO YOU</t>
@@ -170,10 +176,16 @@
     <t xml:space="preserve">Grown at inflation. Replace the input with your real number.</t>
   </si>
   <si>
+    <t xml:space="preserve">What you have today if nothing changes (the bar PLUS your hours here)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corrected Sept 2026. The old version compared this job against the bar alone, which flattered it. Today you have BOTH - the bar and about 24 hours a week here at $30/hr. Going full-time means giving up both, so both belong in the comparison.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cash difference that year</t>
   </si>
   <si>
-    <t xml:space="preserve">Negative early. That is the honest shape of this - you take a pay cut to buy equity in something bigger.</t>
+    <t xml:space="preserve">Zero while you are still part-time, because nothing has changed yet. Negative in the first years after you go full-time. That is the honest shape of this - you take a pay cut to buy equity in something bigger.</t>
   </si>
   <si>
     <t xml:space="preserve">Cumulative cash difference</t>
@@ -186,6 +198,9 @@
   </si>
   <si>
     <t xml:space="preserve">Are you ahead yet?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads 'no change yet' while you are still part-time, because you have not given anything up.</t>
   </si>
   <si>
     <t xml:space="preserve">Scag Scapes - the plan these numbers sit on top of</t>
@@ -1063,7 +1078,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -1200,12 +1215,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B14" s="7" t="n">
-        <v>0.6</v>
+      <c r="B14" s="5" t="n">
+        <v>24</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>23</v>
@@ -1215,11 +1230,22 @@
       <c r="A15" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="8" t="n">
-        <v>2</v>
+      <c r="B15" s="5" t="n">
+        <v>30</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>25</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1239,7 +1265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:R23"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
@@ -1249,7 +1275,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1271,7 +1297,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1333,7 +1359,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="10" t="n">
         <v>1</v>
@@ -1382,12 +1408,12 @@
       </c>
       <c r="Q5" s="2"/>
       <c r="R5" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B6" s="11" t="n">
         <v>1107883.476</v>
@@ -1437,137 +1463,137 @@
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
     </row>
-    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" s="12" t="n">
-        <f aca="false">IF(B6&gt;=6000000,'Your numbers'!$B$7,IF(B6&gt;=3000000,'Your numbers'!$B$6,IF(B6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(1&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
-        <v>57000</v>
+        <f aca="false">IF(1&gt;='Your numbers'!$B$16,IF(B6&gt;=6000000,'Your numbers'!$B$7,IF(B6&gt;=3000000,'Your numbers'!$B$6,IF(B6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
+        <v>37440</v>
       </c>
       <c r="C7" s="12" t="n">
-        <f aca="false">IF(C6&gt;=6000000,'Your numbers'!$B$7,IF(C6&gt;=3000000,'Your numbers'!$B$6,IF(C6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(2&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(2&gt;='Your numbers'!$B$16,IF(C6&gt;=6000000,'Your numbers'!$B$7,IF(C6&gt;=3000000,'Your numbers'!$B$6,IF(C6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>95000</v>
       </c>
       <c r="D7" s="12" t="n">
-        <f aca="false">IF(D6&gt;=6000000,'Your numbers'!$B$7,IF(D6&gt;=3000000,'Your numbers'!$B$6,IF(D6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(3&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(3&gt;='Your numbers'!$B$16,IF(D6&gt;=6000000,'Your numbers'!$B$7,IF(D6&gt;=3000000,'Your numbers'!$B$6,IF(D6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>95000</v>
       </c>
       <c r="E7" s="12" t="n">
-        <f aca="false">IF(E6&gt;=6000000,'Your numbers'!$B$7,IF(E6&gt;=3000000,'Your numbers'!$B$6,IF(E6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(4&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(4&gt;='Your numbers'!$B$16,IF(E6&gt;=6000000,'Your numbers'!$B$7,IF(E6&gt;=3000000,'Your numbers'!$B$6,IF(E6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>120000</v>
       </c>
       <c r="F7" s="12" t="n">
-        <f aca="false">IF(F6&gt;=6000000,'Your numbers'!$B$7,IF(F6&gt;=3000000,'Your numbers'!$B$6,IF(F6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(5&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(5&gt;='Your numbers'!$B$16,IF(F6&gt;=6000000,'Your numbers'!$B$7,IF(F6&gt;=3000000,'Your numbers'!$B$6,IF(F6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>120000</v>
       </c>
       <c r="G7" s="12" t="n">
-        <f aca="false">IF(G6&gt;=6000000,'Your numbers'!$B$7,IF(G6&gt;=3000000,'Your numbers'!$B$6,IF(G6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(6&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(6&gt;='Your numbers'!$B$16,IF(G6&gt;=6000000,'Your numbers'!$B$7,IF(G6&gt;=3000000,'Your numbers'!$B$6,IF(G6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>120000</v>
       </c>
       <c r="H7" s="12" t="n">
-        <f aca="false">IF(H6&gt;=6000000,'Your numbers'!$B$7,IF(H6&gt;=3000000,'Your numbers'!$B$6,IF(H6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(7&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(7&gt;='Your numbers'!$B$16,IF(H6&gt;=6000000,'Your numbers'!$B$7,IF(H6&gt;=3000000,'Your numbers'!$B$6,IF(H6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>155000</v>
       </c>
       <c r="I7" s="12" t="n">
-        <f aca="false">IF(I6&gt;=6000000,'Your numbers'!$B$7,IF(I6&gt;=3000000,'Your numbers'!$B$6,IF(I6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(8&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(8&gt;='Your numbers'!$B$16,IF(I6&gt;=6000000,'Your numbers'!$B$7,IF(I6&gt;=3000000,'Your numbers'!$B$6,IF(I6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>155000</v>
       </c>
       <c r="J7" s="12" t="n">
-        <f aca="false">IF(J6&gt;=6000000,'Your numbers'!$B$7,IF(J6&gt;=3000000,'Your numbers'!$B$6,IF(J6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(9&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(9&gt;='Your numbers'!$B$16,IF(J6&gt;=6000000,'Your numbers'!$B$7,IF(J6&gt;=3000000,'Your numbers'!$B$6,IF(J6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>155000</v>
       </c>
       <c r="K7" s="12" t="n">
-        <f aca="false">IF(K6&gt;=6000000,'Your numbers'!$B$7,IF(K6&gt;=3000000,'Your numbers'!$B$6,IF(K6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(10&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(10&gt;='Your numbers'!$B$16,IF(K6&gt;=6000000,'Your numbers'!$B$7,IF(K6&gt;=3000000,'Your numbers'!$B$6,IF(K6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>155000</v>
       </c>
       <c r="L7" s="12" t="n">
-        <f aca="false">IF(L6&gt;=6000000,'Your numbers'!$B$7,IF(L6&gt;=3000000,'Your numbers'!$B$6,IF(L6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(11&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(11&gt;='Your numbers'!$B$16,IF(L6&gt;=6000000,'Your numbers'!$B$7,IF(L6&gt;=3000000,'Your numbers'!$B$6,IF(L6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>155000</v>
       </c>
       <c r="M7" s="12" t="n">
-        <f aca="false">IF(M6&gt;=6000000,'Your numbers'!$B$7,IF(M6&gt;=3000000,'Your numbers'!$B$6,IF(M6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(12&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(12&gt;='Your numbers'!$B$16,IF(M6&gt;=6000000,'Your numbers'!$B$7,IF(M6&gt;=3000000,'Your numbers'!$B$6,IF(M6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>185000</v>
       </c>
       <c r="N7" s="12" t="n">
-        <f aca="false">IF(N6&gt;=6000000,'Your numbers'!$B$7,IF(N6&gt;=3000000,'Your numbers'!$B$6,IF(N6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(13&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(13&gt;='Your numbers'!$B$16,IF(N6&gt;=6000000,'Your numbers'!$B$7,IF(N6&gt;=3000000,'Your numbers'!$B$6,IF(N6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>185000</v>
       </c>
       <c r="O7" s="12" t="n">
-        <f aca="false">IF(O6&gt;=6000000,'Your numbers'!$B$7,IF(O6&gt;=3000000,'Your numbers'!$B$6,IF(O6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(14&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(14&gt;='Your numbers'!$B$16,IF(O6&gt;=6000000,'Your numbers'!$B$7,IF(O6&gt;=3000000,'Your numbers'!$B$6,IF(O6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>185000</v>
       </c>
       <c r="P7" s="12" t="n">
-        <f aca="false">IF(P6&gt;=6000000,'Your numbers'!$B$7,IF(P6&gt;=3000000,'Your numbers'!$B$6,IF(P6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4)))*IF(15&gt;='Your numbers'!$B$15,1,'Your numbers'!$B$14)</f>
+        <f aca="false">IF(15&gt;='Your numbers'!$B$16,IF(P6&gt;=6000000,'Your numbers'!$B$7,IF(P6&gt;=3000000,'Your numbers'!$B$6,IF(P6&gt;=1500000,'Your numbers'!$B$5,'Your numbers'!$B$4))),'Your numbers'!$B$14*'Your numbers'!$B$15*52)</f>
         <v>185000</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B8" s="12" t="n">
-        <f aca="false">B7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
-        <v>12540</v>
+        <f aca="false">IF(1&lt;'Your numbers'!$B$16,0,B7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
+        <v>0</v>
       </c>
       <c r="C8" s="12" t="n">
-        <f aca="false">C7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(2&lt;'Your numbers'!$B$16,0,C7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>20900</v>
       </c>
       <c r="D8" s="12" t="n">
-        <f aca="false">D7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(3&lt;'Your numbers'!$B$16,0,D7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>20900</v>
       </c>
       <c r="E8" s="12" t="n">
-        <f aca="false">E7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(4&lt;'Your numbers'!$B$16,0,E7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>26400</v>
       </c>
       <c r="F8" s="12" t="n">
-        <f aca="false">F7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(5&lt;'Your numbers'!$B$16,0,F7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>26400</v>
       </c>
       <c r="G8" s="12" t="n">
-        <f aca="false">G7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(6&lt;'Your numbers'!$B$16,0,G7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>26400</v>
       </c>
       <c r="H8" s="12" t="n">
-        <f aca="false">H7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(7&lt;'Your numbers'!$B$16,0,H7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>34100</v>
       </c>
       <c r="I8" s="12" t="n">
-        <f aca="false">I7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(8&lt;'Your numbers'!$B$16,0,I7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>34100</v>
       </c>
       <c r="J8" s="12" t="n">
-        <f aca="false">J7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(9&lt;'Your numbers'!$B$16,0,J7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>34100</v>
       </c>
       <c r="K8" s="12" t="n">
-        <f aca="false">K7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(10&lt;'Your numbers'!$B$16,0,K7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>34100</v>
       </c>
       <c r="L8" s="12" t="n">
-        <f aca="false">L7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(11&lt;'Your numbers'!$B$16,0,L7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>34100</v>
       </c>
       <c r="M8" s="12" t="n">
-        <f aca="false">M7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(12&lt;'Your numbers'!$B$16,0,M7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>40700</v>
       </c>
       <c r="N8" s="12" t="n">
-        <f aca="false">N7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(13&lt;'Your numbers'!$B$16,0,N7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>40700</v>
       </c>
       <c r="O8" s="12" t="n">
-        <f aca="false">O7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(14&lt;'Your numbers'!$B$16,0,O7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>40700</v>
       </c>
       <c r="P8" s="12" t="n">
-        <f aca="false">P7*'Your numbers'!$B$8*'Your numbers'!$B$9</f>
+        <f aca="false">IF(15&lt;'Your numbers'!$B$16,0,P7*'Your numbers'!$B$8*'Your numbers'!$B$9)</f>
         <v>40700</v>
       </c>
       <c r="Q8" s="2"/>
@@ -1575,11 +1601,11 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">B7+B8</f>
-        <v>69540</v>
+        <v>37440</v>
       </c>
       <c r="C9" s="11" t="n">
         <f aca="false">C7+C8</f>
@@ -1642,7 +1668,7 @@
     </row>
     <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B10" s="12" t="n">
         <v>0</v>
@@ -1691,16 +1717,16 @@
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="11" t="n">
         <f aca="false">B9-B10</f>
-        <v>69540</v>
+        <v>37440</v>
       </c>
       <c r="C11" s="11" t="n">
         <f aca="false">C9-C10</f>
@@ -1763,7 +1789,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B12" s="14"/>
       <c r="C12" s="14"/>
@@ -1785,7 +1811,7 @@
     </row>
     <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B13" s="15" t="n">
         <f aca="false">MIN(1,MAX(0,1/'Your numbers'!$B$11))</f>
@@ -1849,12 +1875,12 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B14" s="16" t="n">
         <f aca="false">B13*'Your numbers'!$B$10</f>
@@ -1921,7 +1947,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>737130.151233105</v>
@@ -1973,7 +1999,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B16" s="12" t="n">
         <f aca="false">MAX(0,B15-'Your numbers'!$B$12)</f>
@@ -2040,7 +2066,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">B14*B16</f>
@@ -2107,7 +2133,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="17" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -2129,7 +2155,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B19" s="12" t="n">
         <f aca="false">'Your numbers'!$B$13*(1.0275)^0</f>
@@ -2193,280 +2219,351 @@
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="6" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B20" s="11" t="n">
-        <f aca="false">B9-B19</f>
-        <v>-58835</v>
+        <f aca="false">B19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^0</f>
+        <v>165815</v>
       </c>
       <c r="C20" s="11" t="n">
-        <f aca="false">C9-C19</f>
-        <v>-16005.3125</v>
+        <f aca="false">C19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^1</f>
+        <v>170374.9125</v>
       </c>
       <c r="D20" s="11" t="n">
-        <f aca="false">D9-D19</f>
-        <v>-19632.70859375</v>
+        <f aca="false">D19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^2</f>
+        <v>175060.22259375</v>
       </c>
       <c r="E20" s="11" t="n">
-        <f aca="false">E9-E19</f>
-        <v>7140.14191992185</v>
+        <f aca="false">E19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^3</f>
+        <v>179874.378715078</v>
       </c>
       <c r="F20" s="11" t="n">
-        <f aca="false">F9-F19</f>
-        <v>3310.49582271971</v>
+        <f aca="false">F19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^4</f>
+        <v>184820.924129743</v>
       </c>
       <c r="G20" s="11" t="n">
-        <f aca="false">G9-G19</f>
-        <v>-624.465542155551</v>
+        <f aca="false">G19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^5</f>
+        <v>189903.499543311</v>
       </c>
       <c r="H20" s="11" t="n">
-        <f aca="false">H9-H19</f>
-        <v>38032.3616554352</v>
+        <f aca="false">H19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^6</f>
+        <v>195125.845780752</v>
       </c>
       <c r="I20" s="11" t="n">
-        <f aca="false">I9-I19</f>
-        <v>33878.0016009596</v>
+        <f aca="false">I19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^7</f>
+        <v>200491.806539723</v>
       </c>
       <c r="J20" s="11" t="n">
-        <f aca="false">J9-J19</f>
-        <v>29609.396644986</v>
+        <f aca="false">J19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^8</f>
+        <v>206005.331219565</v>
       </c>
       <c r="K20" s="11" t="n">
-        <f aca="false">K9-K19</f>
-        <v>25223.4050527231</v>
+        <f aca="false">K19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^9</f>
+        <v>211670.477828103</v>
       </c>
       <c r="L20" s="11" t="n">
-        <f aca="false">L9-L19</f>
-        <v>20716.798691673</v>
+        <f aca="false">L19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^10</f>
+        <v>217491.415968376</v>
       </c>
       <c r="M20" s="11" t="n">
-        <f aca="false">M9-M19</f>
-        <v>52686.260655694</v>
+        <f aca="false">M19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^11</f>
+        <v>223472.429907506</v>
       </c>
       <c r="N20" s="11" t="n">
-        <f aca="false">N9-N19</f>
-        <v>47928.3828237256</v>
+        <f aca="false">N19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^12</f>
+        <v>229617.921729963</v>
       </c>
       <c r="O20" s="11" t="n">
-        <f aca="false">O9-O19</f>
-        <v>43039.663351378</v>
+        <f aca="false">O19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^13</f>
+        <v>235932.414577537</v>
       </c>
       <c r="P20" s="11" t="n">
-        <f aca="false">P9-P19</f>
-        <v>38016.5040935409</v>
+        <f aca="false">P19+'Your numbers'!$B$14*'Your numbers'!$B$15*52*(1.0275)^14</f>
+        <v>242420.555978419</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="6" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B21" s="11" t="n">
-        <f aca="false">B20</f>
-        <v>-58835</v>
+        <f aca="false">IF(1&lt;'Your numbers'!$B$16,0,B9-B20)</f>
+        <v>0</v>
       </c>
       <c r="C21" s="11" t="n">
-        <f aca="false">B21+C20</f>
-        <v>-74840.3125</v>
+        <f aca="false">IF(2&lt;'Your numbers'!$B$16,0,C9-C20)</f>
+        <v>-54474.9125</v>
       </c>
       <c r="D21" s="11" t="n">
-        <f aca="false">C21+D20</f>
-        <v>-94473.02109375</v>
+        <f aca="false">IF(3&lt;'Your numbers'!$B$16,0,D9-D20)</f>
+        <v>-59160.2225937501</v>
       </c>
       <c r="E21" s="11" t="n">
-        <f aca="false">D21+E20</f>
-        <v>-87332.8791738282</v>
+        <f aca="false">IF(4&lt;'Your numbers'!$B$16,0,E9-E20)</f>
+        <v>-33474.3787150782</v>
       </c>
       <c r="F21" s="11" t="n">
-        <f aca="false">E21+F20</f>
-        <v>-84022.3833511085</v>
+        <f aca="false">IF(5&lt;'Your numbers'!$B$16,0,F9-F20)</f>
+        <v>-38420.9241297428</v>
       </c>
       <c r="G21" s="11" t="n">
-        <f aca="false">F21+G20</f>
-        <v>-84646.848893264</v>
+        <f aca="false">IF(6&lt;'Your numbers'!$B$16,0,G9-G20)</f>
+        <v>-43503.4995433108</v>
       </c>
       <c r="H21" s="11" t="n">
-        <f aca="false">G21+H20</f>
-        <v>-46614.4872378288</v>
+        <f aca="false">IF(7&lt;'Your numbers'!$B$16,0,H9-H20)</f>
+        <v>-6025.84578075184</v>
       </c>
       <c r="I21" s="11" t="n">
-        <f aca="false">H21+I20</f>
-        <v>-12736.4856368692</v>
+        <f aca="false">IF(8&lt;'Your numbers'!$B$16,0,I9-I20)</f>
+        <v>-11391.8065397225</v>
       </c>
       <c r="J21" s="11" t="n">
-        <f aca="false">I21+J20</f>
-        <v>16872.9110081168</v>
+        <f aca="false">IF(9&lt;'Your numbers'!$B$16,0,J9-J20)</f>
+        <v>-16905.3312195649</v>
       </c>
       <c r="K21" s="11" t="n">
-        <f aca="false">J21+K20</f>
-        <v>42096.3160608399</v>
+        <f aca="false">IF(10&lt;'Your numbers'!$B$16,0,K9-K20)</f>
+        <v>-22570.477828103</v>
       </c>
       <c r="L21" s="11" t="n">
-        <f aca="false">K21+L20</f>
-        <v>62813.1147525129</v>
+        <f aca="false">IF(11&lt;'Your numbers'!$B$16,0,L9-L20)</f>
+        <v>-28391.4159683758</v>
       </c>
       <c r="M21" s="11" t="n">
-        <f aca="false">L21+M20</f>
-        <v>115499.375408207</v>
+        <f aca="false">IF(12&lt;'Your numbers'!$B$16,0,M9-M20)</f>
+        <v>2227.57009249384</v>
       </c>
       <c r="N21" s="11" t="n">
-        <f aca="false">M21+N20</f>
-        <v>163427.758231932</v>
+        <f aca="false">IF(13&lt;'Your numbers'!$B$16,0,N9-N20)</f>
+        <v>-3917.92172996257</v>
       </c>
       <c r="O21" s="11" t="n">
-        <f aca="false">N21+O20</f>
-        <v>206467.42158331</v>
+        <f aca="false">IF(14&lt;'Your numbers'!$B$16,0,O9-O20)</f>
+        <v>-10232.4145775366</v>
       </c>
       <c r="P21" s="11" t="n">
-        <f aca="false">O21+P20</f>
-        <v>244483.925676851</v>
+        <f aca="false">IF(15&lt;'Your numbers'!$B$16,0,P9-P20)</f>
+        <v>-16720.5559784189</v>
       </c>
       <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R21" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B22" s="11" t="n">
-        <f aca="false">B21+B17</f>
-        <v>-58396.5274630069</v>
+        <f aca="false">B21</f>
+        <v>0</v>
       </c>
       <c r="C22" s="11" t="n">
-        <f aca="false">C21+C17</f>
-        <v>-70574.7763450336</v>
+        <f aca="false">B22+C21</f>
+        <v>-54474.9125</v>
       </c>
       <c r="D22" s="11" t="n">
-        <f aca="false">D21+D17</f>
-        <v>-71858.0510298115</v>
+        <f aca="false">C22+D21</f>
+        <v>-113635.13509375</v>
       </c>
       <c r="E22" s="11" t="n">
-        <f aca="false">E21+E17</f>
-        <v>30546.3250731126</v>
+        <f aca="false">D22+E21</f>
+        <v>-147109.513808828</v>
       </c>
       <c r="F22" s="11" t="n">
-        <f aca="false">F21+F17</f>
-        <v>43107.0386743519</v>
+        <f aca="false">E22+F21</f>
+        <v>-185530.437938571</v>
       </c>
       <c r="G22" s="11" t="n">
-        <f aca="false">G21+G17</f>
-        <v>78100.1896970572</v>
+        <f aca="false">F22+G21</f>
+        <v>-229033.937481882</v>
       </c>
       <c r="H22" s="11" t="n">
-        <f aca="false">H21+H17</f>
-        <v>201347.647362505</v>
+        <f aca="false">G22+H21</f>
+        <v>-235059.783262634</v>
       </c>
       <c r="I22" s="11" t="n">
-        <f aca="false">I21+I17</f>
-        <v>330728.981968184</v>
+        <f aca="false">H22+I21</f>
+        <v>-246451.589802356</v>
       </c>
       <c r="J22" s="11" t="n">
-        <f aca="false">J21+J17</f>
-        <v>433112.285448631</v>
+        <f aca="false">I22+J21</f>
+        <v>-263356.921021921</v>
       </c>
       <c r="K22" s="11" t="n">
-        <f aca="false">K21+K17</f>
-        <v>575580.862519666</v>
+        <f aca="false">J22+K21</f>
+        <v>-285927.398850024</v>
       </c>
       <c r="L22" s="11" t="n">
-        <f aca="false">L21+L17</f>
-        <v>965594.251979523</v>
+        <f aca="false">K22+L21</f>
+        <v>-314318.8148184</v>
       </c>
       <c r="M22" s="11" t="n">
-        <f aca="false">M21+M17</f>
-        <v>1197564.30855157</v>
+        <f aca="false">L22+M21</f>
+        <v>-312091.244725906</v>
       </c>
       <c r="N22" s="11" t="n">
-        <f aca="false">N21+N17</f>
-        <v>1439095.62604909</v>
+        <f aca="false">M22+N21</f>
+        <v>-316009.166455869</v>
       </c>
       <c r="O22" s="11" t="n">
-        <f aca="false">O21+O17</f>
-        <v>1607986.76556719</v>
+        <f aca="false">N22+O21</f>
+        <v>-326241.581033405</v>
       </c>
       <c r="P22" s="11" t="n">
-        <f aca="false">P21+P17</f>
-        <v>1772372.8358234</v>
+        <f aca="false">O22+P21</f>
+        <v>-342962.137011824</v>
       </c>
       <c r="Q22" s="2"/>
-      <c r="R22" s="6" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B23" s="19" t="str">
-        <f aca="false">IF(B22&gt;0,"AHEAD","behind")</f>
+      <c r="R22" s="2"/>
+    </row>
+    <row r="23" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="B23" s="11" t="n">
+        <f aca="false">B22+B17</f>
+        <v>438.472536993149</v>
+      </c>
+      <c r="C23" s="11" t="n">
+        <f aca="false">C22+C17</f>
+        <v>-50209.3763450336</v>
+      </c>
+      <c r="D23" s="11" t="n">
+        <f aca="false">D22+D17</f>
+        <v>-91020.1650298116</v>
+      </c>
+      <c r="E23" s="11" t="n">
+        <f aca="false">E22+E17</f>
+        <v>-29230.3095618874</v>
+      </c>
+      <c r="F23" s="11" t="n">
+        <f aca="false">F22+F17</f>
+        <v>-58401.0159131107</v>
+      </c>
+      <c r="G23" s="11" t="n">
+        <f aca="false">G22+G17</f>
+        <v>-66286.8988915606</v>
+      </c>
+      <c r="H23" s="11" t="n">
+        <f aca="false">H22+H17</f>
+        <v>12902.3513377004</v>
+      </c>
+      <c r="I23" s="11" t="n">
+        <f aca="false">I22+I17</f>
+        <v>97013.877802697</v>
+      </c>
+      <c r="J23" s="11" t="n">
+        <f aca="false">J22+J17</f>
+        <v>152882.453418593</v>
+      </c>
+      <c r="K23" s="11" t="n">
+        <f aca="false">K22+K17</f>
+        <v>247557.147608802</v>
+      </c>
+      <c r="L23" s="11" t="n">
+        <f aca="false">L22+L17</f>
+        <v>588462.322408611</v>
+      </c>
+      <c r="M23" s="11" t="n">
+        <f aca="false">M22+M17</f>
+        <v>769973.688417454</v>
+      </c>
+      <c r="N23" s="11" t="n">
+        <f aca="false">N22+N17</f>
+        <v>959658.701361291</v>
+      </c>
+      <c r="O23" s="11" t="n">
+        <f aca="false">O22+O17</f>
+        <v>1075277.76295047</v>
+      </c>
+      <c r="P23" s="11" t="n">
+        <f aca="false">P22+P17</f>
+        <v>1184926.77313473</v>
+      </c>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="19" t="str">
+        <f aca="false">IF(1&lt;'Your numbers'!$B$16,"no change yet",IF(B23&gt;0,"AHEAD","behind"))</f>
+        <v>no change yet</v>
+      </c>
+      <c r="C24" s="19" t="str">
+        <f aca="false">IF(2&lt;'Your numbers'!$B$16,"no change yet",IF(C23&gt;0,"AHEAD","behind"))</f>
         <v>behind</v>
       </c>
-      <c r="C23" s="19" t="str">
-        <f aca="false">IF(C22&gt;0,"AHEAD","behind")</f>
+      <c r="D24" s="19" t="str">
+        <f aca="false">IF(3&lt;'Your numbers'!$B$16,"no change yet",IF(D23&gt;0,"AHEAD","behind"))</f>
         <v>behind</v>
       </c>
-      <c r="D23" s="19" t="str">
-        <f aca="false">IF(D22&gt;0,"AHEAD","behind")</f>
+      <c r="E24" s="19" t="str">
+        <f aca="false">IF(4&lt;'Your numbers'!$B$16,"no change yet",IF(E23&gt;0,"AHEAD","behind"))</f>
         <v>behind</v>
       </c>
-      <c r="E23" s="19" t="str">
-        <f aca="false">IF(E22&gt;0,"AHEAD","behind")</f>
+      <c r="F24" s="19" t="str">
+        <f aca="false">IF(5&lt;'Your numbers'!$B$16,"no change yet",IF(F23&gt;0,"AHEAD","behind"))</f>
+        <v>behind</v>
+      </c>
+      <c r="G24" s="19" t="str">
+        <f aca="false">IF(6&lt;'Your numbers'!$B$16,"no change yet",IF(G23&gt;0,"AHEAD","behind"))</f>
+        <v>behind</v>
+      </c>
+      <c r="H24" s="19" t="str">
+        <f aca="false">IF(7&lt;'Your numbers'!$B$16,"no change yet",IF(H23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="F23" s="19" t="str">
-        <f aca="false">IF(F22&gt;0,"AHEAD","behind")</f>
+      <c r="I24" s="19" t="str">
+        <f aca="false">IF(8&lt;'Your numbers'!$B$16,"no change yet",IF(I23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="G23" s="19" t="str">
-        <f aca="false">IF(G22&gt;0,"AHEAD","behind")</f>
+      <c r="J24" s="19" t="str">
+        <f aca="false">IF(9&lt;'Your numbers'!$B$16,"no change yet",IF(J23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="H23" s="19" t="str">
-        <f aca="false">IF(H22&gt;0,"AHEAD","behind")</f>
+      <c r="K24" s="19" t="str">
+        <f aca="false">IF(10&lt;'Your numbers'!$B$16,"no change yet",IF(K23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="I23" s="19" t="str">
-        <f aca="false">IF(I22&gt;0,"AHEAD","behind")</f>
+      <c r="L24" s="19" t="str">
+        <f aca="false">IF(11&lt;'Your numbers'!$B$16,"no change yet",IF(L23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="J23" s="19" t="str">
-        <f aca="false">IF(J22&gt;0,"AHEAD","behind")</f>
+      <c r="M24" s="19" t="str">
+        <f aca="false">IF(12&lt;'Your numbers'!$B$16,"no change yet",IF(M23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="K23" s="19" t="str">
-        <f aca="false">IF(K22&gt;0,"AHEAD","behind")</f>
+      <c r="N24" s="19" t="str">
+        <f aca="false">IF(13&lt;'Your numbers'!$B$16,"no change yet",IF(N23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="L23" s="19" t="str">
-        <f aca="false">IF(L22&gt;0,"AHEAD","behind")</f>
+      <c r="O24" s="19" t="str">
+        <f aca="false">IF(14&lt;'Your numbers'!$B$16,"no change yet",IF(O23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="M23" s="19" t="str">
-        <f aca="false">IF(M22&gt;0,"AHEAD","behind")</f>
+      <c r="P24" s="19" t="str">
+        <f aca="false">IF(15&lt;'Your numbers'!$B$16,"no change yet",IF(P23&gt;0,"AHEAD","behind"))</f>
         <v>AHEAD</v>
       </c>
-      <c r="N23" s="19" t="str">
-        <f aca="false">IF(N22&gt;0,"AHEAD","behind")</f>
-        <v>AHEAD</v>
-      </c>
-      <c r="O23" s="19" t="str">
-        <f aca="false">IF(O22&gt;0,"AHEAD","behind")</f>
-        <v>AHEAD</v>
-      </c>
-      <c r="P23" s="19" t="str">
-        <f aca="false">IF(P22&gt;0,"AHEAD","behind")</f>
-        <v>AHEAD</v>
-      </c>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="6" t="s">
+        <v>58</v>
+      </c>
     </row>
   </sheetData>
   <sheetProtection sheet="true" password="ef11" formatCells="false" formatColumns="false" formatRows="false"/>
@@ -2495,7 +2592,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2517,7 +2614,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2559,7 +2656,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="20" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -2601,7 +2698,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B6" s="10" t="n">
         <v>1</v>
@@ -2650,12 +2747,12 @@
       </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B7" s="11" t="n">
         <v>1107883.476</v>
@@ -2707,7 +2804,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B8" s="21" t="n">
         <v>2</v>
@@ -2759,7 +2856,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B9" s="19" t="n">
         <v>9</v>
@@ -2811,7 +2908,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B10" s="11" t="n">
         <v>309346.07309104</v>
@@ -2860,12 +2957,12 @@
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="6" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B11" s="12" t="n">
         <v>61038.4292364159</v>
@@ -2917,7 +3014,7 @@
     </row>
     <row r="12" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B12" s="11" t="n">
         <v>737130.151233105</v>
@@ -2966,7 +3063,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -2996,7 +3093,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -3018,7 +3115,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3060,14 +3157,14 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="B4" s="7" t="n">
         <v>0.2</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="20" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
@@ -3086,14 +3183,14 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B5" s="7" t="n">
         <v>0.0875</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="20" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
@@ -3152,7 +3249,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="10" t="n">
         <v>1</v>
@@ -3201,12 +3298,12 @@
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B9" s="11" t="n">
         <f aca="false">'Year by year'!B17</f>
@@ -3270,12 +3367,12 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="6" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="B10" s="11" t="n">
         <f aca="false">B9*(1-$B$4)</f>
@@ -3342,7 +3439,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B11" s="12" t="n">
         <f aca="false">B10</f>
@@ -3409,7 +3506,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B12" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,36,-B10))</f>
@@ -3476,7 +3573,7 @@
     </row>
     <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="B13" s="11" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,60,-B10))</f>
@@ -3540,12 +3637,12 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="6" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="B14" s="12" t="n">
         <f aca="false">IF(B10=0,0,PMT($B$5/12,84,-B10))</f>
@@ -3612,7 +3709,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -3634,7 +3731,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="B16" s="12" t="n">
         <v>309346.07309104</v>
@@ -3686,7 +3783,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="B17" s="12" t="n">
         <v>61038.4292364159</v>
@@ -3738,7 +3835,7 @@
     </row>
     <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="B18" s="16" t="n">
         <f aca="false">IF(B16=0,0,B13*12/B16)</f>
@@ -3802,12 +3899,12 @@
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="6" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="4" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="B19" s="19" t="str">
         <f aca="false">IF(B10=0,"-",IF(B17&gt;=B10,"yes","no - needs a note"))</f>
@@ -3894,7 +3991,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="17" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -3916,7 +4013,7 @@
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="22" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -3938,7 +4035,7 @@
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="22" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B23" s="22"/>
       <c r="C23" s="22"/>
@@ -3960,7 +4057,7 @@
     </row>
     <row r="24" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="22" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B24" s="22"/>
       <c r="C24" s="22"/>
@@ -3982,7 +4079,7 @@
     </row>
     <row r="25" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -4004,7 +4101,7 @@
     </row>
     <row r="26" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="22" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B26" s="22"/>
       <c r="C26" s="22"/>
@@ -4026,7 +4123,7 @@
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="22" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B27" s="22"/>
       <c r="C27" s="22"/>
@@ -4081,14 +4178,14 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4100,75 +4197,75 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="24" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="C6" s="25" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="24" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C7" s="25" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="24" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="24" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="24" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C10" s="25" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4178,75 +4275,75 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="27"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="24" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C14" s="25" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="24" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C15" s="25" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="24" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C16" s="25" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="24" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C17" s="25" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="24" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B18" s="25" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C18" s="25" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4256,86 +4353,86 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="28" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B20" s="29"/>
       <c r="C20" s="29"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="23" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="B21" s="23" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C21" s="23" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="24" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B22" s="25" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="C22" s="25" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="24" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B23" s="25" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C23" s="25" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="24" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B24" s="25" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C24" s="25" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="24" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B25" s="25" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C25" s="25" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="24" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C26" s="25" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="24" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="B27" s="25" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="C27" s="25" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4345,62 +4442,62 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B29" s="29"/>
       <c r="C29" s="29"/>
     </row>
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B30" s="30" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="C30" s="30"/>
     </row>
     <row r="31" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B31" s="30" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="C31" s="30"/>
     </row>
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B32" s="30" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C32" s="30"/>
     </row>
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B33" s="30" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="C33" s="30"/>
     </row>
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B34" s="30" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="C34" s="30"/>
     </row>
     <row r="35" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="B35" s="30" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C35" s="30"/>
     </row>
@@ -4411,7 +4508,7 @@
     </row>
     <row r="37" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="31" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B37" s="31"/>
       <c r="C37" s="31"/>
@@ -4423,7 +4520,7 @@
     </row>
     <row r="39" customFormat="false" ht="39" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="31" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="B39" s="31"/>
       <c r="C39" s="31"/>
@@ -4435,7 +4532,7 @@
     </row>
     <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="31" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="B41" s="31"/>
       <c r="C41" s="31"/>
